--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mentorship" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funders" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaborators" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funders" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +80,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,7 +641,6 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -661,20 +666,16 @@
           <t>https://osf.io/chje7/overview?view_only=ed137660b3e74abab321ee214a323c35</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>preprint</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -712,26 +713,21 @@
           <t>https://doi.org/10.1016/j.chbah.2026.100261</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>https://osf.io/26yr5/overview?view_only=5b208c266b824f8eb105bed9dad4739a</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,22 +765,16 @@
           <t>https://doi.org/10.1044/2025_JSLHR-25-00294</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -822,22 +812,16 @@
           <t>https://doi.org/10.1016/j.bandl.2026.105723</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -875,22 +859,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2026.121987</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -928,22 +906,16 @@
           <t>https://doi.org/10.1371/journal.pone.0327529</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -991,20 +963,16 @@
           <t>https://osf.io/9b8pq/overview?view_only=360d32c442e4440e89859d379192043a</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>preprint</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1022,7 +990,6 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -1048,20 +1015,16 @@
           <t>https://osf.io/qgrva/overview?view_only=2a4d21db2419426299af9229e8945675</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>preprint</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1099,16 +1062,11 @@
           <t>https://doi.org/10.3758/s13428-025-02608-3</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>seed</t>
@@ -1156,22 +1114,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2025.121253</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1199,18 +1151,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>seed</t>
@@ -1258,22 +1203,16 @@
           <t>https://doi.org/10.1038/s41597-025-06110-5</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1301,24 +1240,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1356,22 +1287,16 @@
           <t>https://doi.org/10.1044/2025_JSLHR-24-00849</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1409,22 +1334,16 @@
           <t>https://doi.org/10.1186/s40359-025-03522-1</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1452,24 +1371,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1497,24 +1408,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1552,26 +1455,21 @@
           <t>https://doi.org/10.3791/66913</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://www.jove.com/v/66913</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1614,15 +1512,11 @@
           <t>https://www.isca-archive.org/speechprosody_2024/chen24c_speechprosody.pdf</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>conference</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>seed</t>
@@ -1670,22 +1564,16 @@
           <t>https://doi.org/10.1016/j.aip.2024.102167</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1723,22 +1611,16 @@
           <t>https://doi.org/10.1016/j.tics.2024.08.005</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1776,22 +1658,16 @@
           <t>https://doi.org/10.3390/brainsci14030264</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1819,24 +1695,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1864,24 +1732,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1909,18 +1769,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>seed</t>
@@ -1958,18 +1811,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>seed</t>
@@ -2007,18 +1853,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>seed</t>
@@ -2046,7 +1885,6 @@
           <t>Wenjun Chen; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -2072,20 +1910,16 @@
           <t>https://osf.io/3c7rd/overview?view_only=a194fd9070ad4ca18b2eb7d5c4d303f4</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>preprint</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2113,7 +1947,6 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>https://jfl.shisu.edu.cn/cn/article/id/729?viewType=HTML</t>
@@ -2124,15 +1957,11 @@
           <t>https://jfl.shisu.edu.cn/cn/article/pdf/preview/729.pdf</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>seed</t>
@@ -2180,22 +2009,16 @@
           <t>https://doi.org/10.3390/brainsci13121724</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2233,22 +2056,16 @@
           <t>https://doi.org/10.1007/s10919-023-00428-7</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2276,18 +2093,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>seed</t>
@@ -2335,22 +2145,16 @@
           <t>https://doi.org/10.3389/fpsyg.2022.1028106</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2388,22 +2192,16 @@
           <t>https://doi.org/10.1016/j.cortex.2021.12.017</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2441,22 +2239,16 @@
           <t>https://doi.org/10.1177/0022022121990897</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2484,24 +2276,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2539,22 +2323,16 @@
           <t>https://doi.org/10.1080/17470919.2021.1938667</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2592,22 +2370,16 @@
           <t>https://doi.org/10.1177/1747021819865833</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2635,18 +2407,11 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>seed</t>
@@ -2694,22 +2459,16 @@
           <t>https://doi.org/10.1016/j.lingua.2026.104185</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2727,7 +2486,6 @@
           <t>Tianze Xu; Xiaoming Jiang; Volker Dellwo</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -2743,22 +2501,16 @@
           <t>https://doi.org/10.31234/osf.io/4zrwy_v3</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2796,22 +2548,16 @@
           <t>https://doi.org/10.3390/languages10060119</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2849,22 +2595,16 @@
           <t>https://doi.org/10.1121/10.0032400</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2902,22 +2642,16 @@
           <t>https://doi.org/10.3390/bs14080686</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2955,22 +2689,16 @@
           <t>https://doi.org/10.1057/s41599-024-03502-7</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3008,22 +2736,16 @@
           <t>https://doi.org/10.1044/2024_JSLHR-23-00553</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3061,22 +2783,16 @@
           <t>https://doi.org/10.20944/preprints202303.0517.v1</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3114,22 +2830,16 @@
           <t>https://doi.org/10.1007/s12144-022-03528-7</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3167,22 +2877,16 @@
           <t>https://doi.org/10.3389/fpsyg.2023.1289045</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3220,22 +2924,16 @@
           <t>https://doi.org/10.1016/j.actpsy.2023.103955</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3273,22 +2971,16 @@
           <t>https://doi.org/10.1038/s41597-022-01811-7</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3326,22 +3018,16 @@
           <t>https://doi.org/10.1016/j.jneuroling.2023.101143</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3379,22 +3065,16 @@
           <t>https://doi.org/10.1016/j.pragma.2023.07.005</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3432,22 +3112,16 @@
           <t>https://doi.org/10.1073/pnas.2111091119</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3485,22 +3159,16 @@
           <t>https://doi.org/10.21437/Interspeech.2022-10531</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3538,22 +3206,16 @@
           <t>https://doi.org/10.1073/pnas.2213828119</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3581,24 +3243,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3636,22 +3290,16 @@
           <t>https://doi.org/10.1109/ISCSLP57327.2022.10037951</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3689,22 +3337,16 @@
           <t>https://doi.org/10.1007/s42761-022-00128-3</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3742,22 +3384,16 @@
           <t>https://doi.org/10.1016/j.pscychresns.2022.111489</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3795,22 +3431,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2022.108254</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3848,22 +3478,16 @@
           <t>https://doi.org/10.3389/fnins.2022.953315</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3901,22 +3525,16 @@
           <t>https://doi.org/10.3758/s13415-020-00849-7</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3929,7 +3547,6 @@
           <t>An alternative structure rescues failed semantics? Strong global expectancy reduces local-mismatch N400 in Chinese flexible structures</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Neuropsychologia</t>
@@ -3950,22 +3567,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2020.107380</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4003,22 +3614,16 @@
           <t>https://doi.org/10.1080/23273798.2020.1781213</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4056,22 +3661,16 @@
           <t>https://doi.org/10.1016/j.brainres.2020.146855</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4109,22 +3708,16 @@
           <t>https://doi.org/10.1016/j.biopsycho.2020.107909</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4137,7 +3730,6 @@
           <t>Eye Movements Reveal Delayed Use of Construction-Based Pragmatic Information During Online Sentence Reading: A Case of Chinese Lian…dou Construction</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Frontiers in Psychology</t>
@@ -4158,22 +3750,16 @@
           <t>https://doi.org/10.3389/fpsyg.2019.02211</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4186,7 +3772,6 @@
           <t>Commentary: A Neural Mechanism of Social Categorization</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Frontiers in Neuroscience</t>
@@ -4207,22 +3792,16 @@
           <t>https://doi.org/10.3389/fnins.2019.00368</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4235,7 +3814,6 @@
           <t>Single-trial Based EEG Classification of the Dynamic Representation of Speaker Stance: A Preliminary Study with Representational Similarity Analysis</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>NeuroManagement and Intelligent Computing Method on Multimodal Interaction on - ICMI '19</t>
@@ -4256,22 +3834,16 @@
           <t>https://doi.org/10.1145/3357160.3357672</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4309,22 +3881,16 @@
           <t>https://doi.org/10.31234/osf.io/8dr23</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4362,22 +3928,16 @@
           <t>https://doi.org/10.1016/j.specom.2018.06.004</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4415,22 +3975,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2018.07.042</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4468,22 +4022,16 @@
           <t>https://doi.org/10.21437/SpeechProsody.2018-55</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4521,22 +4069,16 @@
           <t>https://doi.org/10.1002/hbm.23630</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4574,22 +4116,16 @@
           <t>https://doi.org/10.1016/j.snb.2017.01.052</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4627,22 +4163,16 @@
           <t>https://doi.org/10.1016/j.bandl.2017.04.005</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4680,22 +4210,16 @@
           <t>https://doi.org/10.1002/hbm.23633</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4733,22 +4257,16 @@
           <t>https://doi.org/10.1016/j.specom.2017.01.011</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4786,22 +4304,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2015.12.008</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4839,22 +4351,16 @@
           <t>https://doi.org/10.1037/xhp0000240</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4892,22 +4398,16 @@
           <t>https://doi.org/10.1037/xhp0000043</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4945,22 +4445,16 @@
           <t>https://doi.org/10.1016/j.cortex.2015.02.002</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4998,22 +4492,16 @@
           <t>https://doi.org/10.1080/23273798.2015.1005636</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5051,22 +4539,16 @@
           <t>https://doi.org/10.3389/fnhum.2014.00873</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5104,22 +4586,16 @@
           <t>https://doi.org/10.1093/scan/nst091</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5147,24 +4623,16 @@
           <t>conference-paper</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5202,22 +4670,16 @@
           <t>https://doi.org/10.1016/j.brainres.2012.10.042</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5255,22 +4717,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.06.009</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5308,22 +4764,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.07.021</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5361,22 +4811,16 @@
           <t>https://doi.org/10.1016/j.bandc.2012.11.002</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5414,22 +4858,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2012.04.016</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5467,22 +4905,16 @@
           <t>https://doi.org/10.1016/j.neuroscience.2011.10.035</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5520,22 +4952,16 @@
           <t>https://doi.org/10.1016/j.brainres.2011.06.061</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5573,22 +4999,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2010.02.001</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5626,22 +5046,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.01.013</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5679,22 +5093,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.02.020</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6168,301 +5576,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>at_the_time</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>now</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>show</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>undergraduate / master / phd</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Family, Given</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>their position when mentored</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>year range</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>project/thesis title (zh + en welcome)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>link to thesis/project</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>current position</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>undergraduate</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ge, Jingyi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Undergraduate, SISU</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2022–2024</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>人工智能时代下的跨文化中文语音感知 / Cross-cultural Chinese Voice Perception in the Age of AI</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://shcxcy.usst.edu.cn/shcx/shcx/Index/ItemDetail?id=cd1a87d7-ed37-40f6-8213-fa5b64232282&amp;_LXYear=2024</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MSocSc (Psychology), HKU</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>logo_path</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tooltip</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>show</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Funder/affiliation name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>filename in assets/images/logos/</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Hover tooltip</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>e.g. 2024-2028</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>External URL (optional)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>国家自然科学基金 (NSFC) | NSFC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nsfc.svg</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>国家自然科学基金面上项目 | NSFC General Program</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://www.nsfc.gov.cn/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>上海市哲学社会科学规划 | Shanghai Philosophy &amp; Social Sci.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>shanghai-philosophy.svg</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shanghai Municipal Philosophy and Social Sciences Planning Project</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6727,4 +5840,479 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>affiliation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bio</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>key / emerging</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>display order (0,1,2...)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Full name with title</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Their primary affiliation</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Homepage / Google Scholar / ORCID (optional)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1-3 sentence description of the collaboration / shared work</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prof. Marc D. Pell</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>McGill University, Canada</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.mcgill.ca/scsd/marc-pell</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>My longest-standing collaborator, co-authoring seminal work on vocal emotion, social pragmatics, and dynamic social impression formation from voice (e.g., Trends in Cognitive Sciences 2024, Cortex 2022). Several of my former and visiting students — including Wenjun Chen and Shuyi Zhang — are currently pursuing their PhD under his supervision, fostering ongoing academic inheritance.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prof. Jixing Li</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://jixing-li.github.io/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A key collaborator on neuroimaging studies of naturalistic language processing. We have published in NeuroImage and are developing a large-scale neural database using naturalistic paradigms — a dataset with MEG/fMRI recordings of natural language listening, with annotated text and speaker information, recently submitted to Scientific Data.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prof. Mingya Liu</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Humboldt-Universität zu Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.angl.hu-berlin.de/department/staff-faculty/professors/liu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Collaborator on cross-cultural studies of formal-pragmatic communication and social cognition, with a focus on the formal-linguistic encoding of social cues (e.g., counter-expectational markers) in multilingual contexts.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>emerging</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tianze Xu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PhD candidate, ETH Zürich</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Co-authored work on fMRI computational modeling of naturalistic language processing (NeuroImage 2025).</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>emerging</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yi Li</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PhD candidate, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Collaborator on sound-symbolic association studies (Humanities and Social Sciences Communications 2024; Scientific Reports 2025).</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>emerging</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wenjun Chen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PhD candidate, McGill University</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://wenjunchen29.github.io/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Co-authored work on AI-cloned voice encoding/decoding using EEG (JoVE 2024, Speech Prosody 2024, and ongoing).</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>logo_path</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>tooltip</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Funder name (Chinese + English)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>filename in assets/images/logos/ (or blank for text-only)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Hover tooltip with project details if any</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>e.g. 2023-2026 or ongoing</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>External URL (optional)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>国家自然科学基金 / NSFC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nsfc.png</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>国家自然科学基金面上项目 (NSFC General Program)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.nsfc.gov.cn/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>国家社科基金 / NSSFC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nssfc.png</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>国家社科基金重大项目（参与）/ National Social Science Fund of China (Major Project, participated)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://www.nopss.gov.cn/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上海市科学技术委员会 / STCSM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Shanghai Science and Technology Commission — Shanghai Sci-tech Co-research Program</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://stcsm.sh.gov.cn/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -5429,7 +5429,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[请填写教育背景 / Education to be filled]</t>
+          <t>PhD, Peking University (2005–2010) | Undergraduate, East China Normal University (2001–2005) | Postdoc, Peking University (2010–2012) | Postdoc / Research Associate / Visiting Professor, McGill University (2013–2018) | Associate Professor, Tongji University (2018–2020) | Professor, SISU – Institute of Linguistics (2020–2024) | Professor, SISU – Institute of Language Sciences (2024–present)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5452,9 +5452,14 @@
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=iF2CM7sAAAAJ&amp;hl=en</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ilas.shisu.edu.cn/jxm_10942/list.htm</t>
+          <t>https://ilas.shisu.edu.cn/21/0f/c18209a205071/page.htm</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -5514,26 +5519,10 @@
           <t>Psycholinguistics &amp; Neurolinguistics｜MTL · BrowserPsyLab</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>硕士期间研究嗓音克隆与说话人感知，开发 ZhCDN-24-HAI 语料库。</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MA research on voice cloning and speaker perception. Developed the ZhCDN-24-HAI corpus.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>BA, Heilongjiang University | MA, SISU | PhD, McGill</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Voice cloning, Speaker identification, Speech perception</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0000-0003-3870-5041</t>
@@ -5551,12 +5540,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>PhD Student, McGill University (with Marc Pell)</t>
+          <t>PhD Student, McGill University (2024–2028, with Marc Pell)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2021–2024</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -6290,7 +6279,6 @@
           <t>上海市科学技术委员会 / STCSM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Shanghai Science and Technology Commission — Shanghai Sci-tech Co-research Program</t>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -5115,7 +5115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5468,92 +5468,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>alumni-wenjun-chen</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>alumni</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>陈文均</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Wenjun Chen</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>硕士研究生</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MA Student</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>心理与神经语言学｜MTL · BrowserPsyLab</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Psycholinguistics &amp; Neurolinguistics｜MTL · BrowserPsyLab</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0000-0003-3870-5041</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?user=MOPUcx8AAAAJ</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://wenjunchen29.github.io/</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>PhD Student, McGill University (2024–2028, with Marc Pell)</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2021–2024</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaborators" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funders" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Publications" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="People" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Projects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Collaborators" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Funders" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="News" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5115,7 +5116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5139,7 +5140,8 @@
     <col width="36" customWidth="1" min="19" max="19"/>
     <col width="32" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5250,6 +5252,16 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>next_position</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>show</t>
         </is>
       </c>
@@ -5360,7 +5372,17 @@
           <t>e.g. 2021-2024 (alumni only)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD (alumni only)</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>Position upon leaving (alumni only)</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>yes/no</t>
         </is>
@@ -5462,7 +5484,7 @@
           <t>https://ilas.shisu.edu.cn/21/0f/c18209a205071/page.htm</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6217,4 +6239,330 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tag_zh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tag_en</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>title_zh</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>title_en</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>summary_zh</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>body_zh</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>body_en</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD or YYYY-MM</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>yes / blank (highlight on home sidebar)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Chinese tag (e.g. 国际合作招募)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>English tag</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Chinese title</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>English title</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Chinese summary (shown on home sidebar)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>English summary</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Chinese body (full text on News page)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>English body</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>External link (optional)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>国际合作招募</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Int'l Recruitment</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上海市国际合作研究项目 2026 年度招募外籍青年学者</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026 Shanghai Sci-tech Co-research Program: call for foreign young scientists</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>面向 45 岁以下外籍青年学者，单项资助 40 万人民币，资助期 2 年。课题组优先合作方向：言语情绪、神经语用、跨语言认知。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Open to foreign scientists under 45. Each project funded at RMB 400,000 over 2 years. Priority areas: vocal emotion, neuropragmatics, cross-linguistic cognition.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>由上海市科学技术委员会（STCSM）发布，面向全球 45 岁以下、在海外高校或研究机构任职的青年学者。项目期内需在上海累计驻留不少于 6 个月（含一次连续 3 个月）。申请期：2026 年 1 月 28 日 9:00 — 2026 年 12 月 31 日 16:30（北京时间）。课题组提供合作方案打磨、签证及行政支持。意向合作请直接邮件联系蒋晓鸣教授。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Released by the Shanghai Science and Technology Commission (STCSM). Eligible to foreign scientists under 45 holding a position at an overseas university or research institute. Requires a cumulative 6-month stay in Shanghai (with one continuous 3-month block) during the project. Application window: 9:00 28 Jan 2026 — 16:30 31 Dec 2026 (Beijing time). The lab provides proposal-shaping, visa and administrative support — write directly to Prof. Jiang to discuss.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://xiaomingjiang.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>博士招生</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ph.D. Admissions</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>中国研究 (CSP) 博士奖学金：持续招收国际博士生</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>China Studies Program (CSP) Ph.D. Fellowship: ongoing intake</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>面向国际申请者的全额博士奖学金，研究方向涵盖心理语言学、神经语言学、跨文化交际等。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fully-funded Ph.D. scholarship for international applicants in psycholinguistics, neurolinguistics, and intercultural communication.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>申请人须具备相关学科本科或硕士背景，提交研究计划与推荐信。课题组每年接收 1–2 名 CSP 博士生。具体申请流程请参考上外研究生院相关页面，意向请提前邮件联系。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Applicants should hold a relevant Bachelor's/Master's degree and submit a research proposal with letters of recommendation. The lab accepts 1–2 CSP fellows per year. See SISU Graduate School pages for the formal process; please email in advance to express interest.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://xiaomingjiang.wordpress.com/looking-for-a-phd-through-2022-2023-china-studies-program-csp-ph-d-fellowship/</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>学术活动</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>中国心理语言学年会 (China Psycholinguistics Annual Conference)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>China Psycholinguistics Annual Conference</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>上外语言科学研究院定期承办的国内顶级心理语言学学术会议。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The leading domestic psycholinguistics meeting, regularly hosted by SISU ILAS.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>课题组成员积极参与会议组织与报告，欢迎合作者联系交流。</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lab members are actively involved in organization and presentations; collaborators are welcome to get in touch.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -5114,7 +5114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5204,57 +5204,67 @@
           <t>education</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>education_zh</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>research_areas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>research_areas_zh</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>orcid</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>scholar</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>homepage</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>now</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>next_position</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>show</t>
         </is>
@@ -5326,57 +5336,57 @@
           <t>Education history (one line each, separated by | )</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Research interests, comma-separated</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>filename in assets/images/people/, e.g. xiaoming-jiang.jpg</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>email (optional)</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>ORCID id</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>homepage URL</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>current position (alumni only)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>e.g. 2021-2024 (alumni only)</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>YYYY-MM-DD (alumni only)</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>Position upon leaving (alumni only)</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>yes/no</t>
         </is>
@@ -5450,35 +5460,45 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>博士，北京大学 (2005–2010) | 本科，华东师范大学 (2001–2005) | 博士后，北京大学 (2010–2012) | 博士后 / 副研究员 / 访问教授，麦吉尔大学 (2013–2018) | 副教授，同济大学 (2018–2020) | 教授，上海外国语大学 语言研究院 (2020–2024) | 教授，上海外国语大学 语言科学研究院 (2024–至今)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Vocal emotion, Neuropragmatics, Speech &amp; speaker perception</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>嗓音情绪、神经语用学、言语与说话人感知</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>xiaoming-jiang.jpg</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>xiaoming.jiang@shisu.edu.cn</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?user=iF2CM7sAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://ilas.shisu.edu.cn/21/0f/c18209a205071/page.htm</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -5807,7 +5807,7 @@
     <row r="1" ht="22.05" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -5867,11 +5867,7 @@
           <t>Homepage / Google Scholar / ORCID (optional)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1-3 sentence description of the collaboration / shared work</t>
-        </is>
-      </c>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>yes/no</t>
@@ -5881,7 +5877,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5899,14 +5895,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.mcgill.ca/scsd/marc-pell</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>My longest-standing collaborator, co-authoring seminal work on vocal emotion, social pragmatics, and dynamic social impression formation from voice (e.g., Trends in Cognitive Sciences 2024, Cortex 2022). Several of my former and visiting students — including Wenjun Chen and Shuyi Zhang — are currently pursuing their PhD under his supervision, fostering ongoing academic inheritance.</t>
-        </is>
-      </c>
+          <t>https://www.mcgill.ca/scsd/marc-d-pell-phd</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5916,7 +5908,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5934,14 +5926,10 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jixing-li.github.io/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>A key collaborator on neuroimaging studies of naturalistic language processing. We have published in NeuroImage and are developing a large-scale neural database using naturalistic paradigms — a dataset with MEG/fMRI recordings of natural language listening, with annotated text and speaker information, recently submitted to Scientific Data.</t>
-        </is>
-      </c>
+          <t>https://lt.cityu.edu.hk/people/academic-staff/li-jixing</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5951,7 +5939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5972,11 +5960,7 @@
           <t>https://www.angl.hu-berlin.de/department/staff-faculty/professors/liu</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Collaborator on cross-cultural studies of formal-pragmatic communication and social cognition, with a focus on the formal-linguistic encoding of social cues (e.g., counter-expectational markers) in multilingual contexts.</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5986,7 +5970,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>emerging</t>
+          <t>early_career</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6002,11 +5986,7 @@
           <t>PhD candidate, ETH Zürich</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Co-authored work on fMRI computational modeling of naturalistic language processing (NeuroImage 2025).</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6016,7 +5996,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>emerging</t>
+          <t>early_career</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6032,11 +6012,7 @@
           <t>PhD candidate, University of Cambridge</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Collaborator on sound-symbolic association studies (Humanities and Social Sciences Communications 2024; Scientific Reports 2025).</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6046,7 +6022,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>emerging</t>
+          <t>early_career</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6067,11 +6043,7 @@
           <t>https://wenjunchen29.github.io/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Co-authored work on AI-cloned voice encoding/decoding using EEG (JoVE 2024, Speech Prosody 2024, and ongoing).</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>yes</t>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,19 @@
       <color rgb="FF1A1A1A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +71,16 @@
         <fgColor rgb="FFFCB813"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00003F88"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCB813"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,6 +109,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,8 +478,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:O85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -463,162 +488,165 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="10"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.05" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>authors</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>doi</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>pdf_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>code_url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>video_url</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>show</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>auto (ORCID)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>yes/no</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>MANUAL override</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>auto (orcid id)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>MANUAL: badge text</t>
         </is>
@@ -632,49 +660,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Human brains implicitly and rapidly distinguish AI from human voices before decoding prosodic meaning</t>
+          <t>Stereotypes vs. general knowledge: How listener-specific expectations shape the processing of counter-expectation meaning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
+          <t>Xun Li; Xiaoming Jiang</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lingua</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.64898/2026.04.08.716483</t>
+          <t>10.1016/j.lingua.2026.104185</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.64898/2026.04.08.716483</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.biorxiv.org/content/10.64898/2026.04.08.716483v1.full.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://osf.io/chje7/overview?view_only=ed137660b3e74abab321ee214a323c35</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>preprint</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.lingua.2026.104185</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,49 +713,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prosodic cues strengthen human-AI voice boundaries: Listeners do not easily perceive human speakers and AI clones as the same person</t>
+          <t>Context-dependent acoustic dimensions underlying voice discrimination: Evidence from interpretable machine learning modeling of human perception</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Computers in Human Behavior: Artificial Humans</t>
-        </is>
-      </c>
+          <t>Tianze Xu; Xiaoming Jiang; Volker Dellwo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>journal-article</t>
+          <t>preprint</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.1016/j.chbah.2026.100261</t>
+          <t>10.31234/osf.io/4zrwy_v3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.chbah.2026.100261</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://osf.io/26yr5/overview?view_only=5b208c266b824f8eb105bed9dad4739a</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.31234/osf.io/4zrwy_v3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -736,17 +762,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Altered Selective Attention or Increased Imagination: Effects of Eye Closure on Vocal Expression Perception</t>
+          <t>Ambiguity in vocal expression perception: Evidence from voice morphing and its electrophysiological correlates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xiaoming Jiang; Renneng Luo; Qi Yang</t>
+          <t>Ruixuan Xu; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Journal of Speech, Language, and Hearing Research</t>
+          <t>NeuroImage</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -756,24 +782,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.1044/2025_JSLHR-25-00294</t>
+          <t>10.1016/j.neuroimage.2026.121987</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1044/2025_JSLHR-25-00294</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuroimage.2026.121987</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -783,17 +815,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temporal expectation in turn-taking: Prosodic cues modulate behavioral and neural signatures of turn-end prediction in conversation</t>
+          <t>Human and AI voice identities evoke shared neural signatures during speaker recognition across changes in speech content and prosody</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yue Ji; Quanjun Song; Xiaoming Jiang; Yan Tan; Wei Chang; Xiaolin Zhou</t>
+          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brain and Language, 275, 105723</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -803,24 +835,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.1016/j.bandl.2026.105723</t>
+          <t>10.1016/j.neuropsychologia.2026.109493</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.bandl.2026.105723</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2026.109493</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -830,17 +868,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ambiguity in vocal expression perception: Evidence from voice morphing and its electrophysiological correlates</t>
+          <t>Altered Selective Attention or Increased Imagination: Effects of Eye Closure on Vocal Expression Perception</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ruoyu Xu; Xiaoming Jiang</t>
+          <t>Xiaoming Jiang; Renneng Luo; Qi Yang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NeuroImage, 121987</t>
+          <t>Journal of Speech, Language, and Hearing Research</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -850,24 +888,30 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.1016/j.neuroimage.2026.121987</t>
+          <t>10.1044/2025_JSLHR-25-00294</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.neuroimage.2026.121987</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1044/2025_JSLHR-25-00294</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -877,111 +921,109 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Speak or shout? Nonverbal vocalizations promote rapid detection of emotions in vocal communication</t>
+          <t>Human brains implicitly and rapidly distinguish AI from human voices before decoding prosodic meaning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marc D. Pell; Hongwei Cui; Yui Mori; Xiaoming Jiang</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PLoS One, e0327529</t>
-        </is>
-      </c>
+          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>journal-article</t>
+          <t>preprint</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0327529</t>
+          <t>10.64898/2026.04.08.716483</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pone.0327529</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.64898/2026.04.08.716483</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Human and AI voice identities evoke shared neural signatures during speaker recognition across changes in speech content and prosody</t>
+          <t>Temporal expectation in turn-taking: prosodic cues modulate behavioral and neural signatures of turn-end prediction in conversation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
+          <t>Yujie Ji; Qingyi Song; Xiaoming Jiang; Yingying Tan; Wenshuo Chang; Xiaolin Zhou</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Neuropsychologia</t>
+          <t>Brain and Language</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.64898/2025.12.22.695263</t>
+          <t>10.1016/j.bandl.2026.105723</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://doi.org/10.64898/2025.12.22.695263</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.biorxiv.org/content/10.64898/2025.12.22.695263v1.full.pdf</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://osf.io/9b8pq/overview?view_only=360d32c442e4440e89859d379192043a</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>preprint</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.bandl.2026.105723</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Does Speech Prosody Shape Social Perception Equally for AI and Human Voices? A 16-Dimension Rating Study</t>
+          <t>Prosodic cues strengthen human-AI voice boundaries: Listeners do not easily perceive human speakers and AI clones as the same person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -989,61 +1031,62 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Computers in Human Behavior: Artificial Humans</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.20944/preprints202510.1492.v1</t>
+          <t>10.1016/j.chbah.2026.100261</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://doi.org/10.20944/preprints202510.1492.v1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.preprints.org/frontend/manuscript/9ccd15a8562792c12b159e8c3f0c7aa8/download_pub</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://osf.io/qgrva/overview?view_only=2a4d21db2419426299af9229e8945675</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>preprint</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.chbah.2026.100261</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Introducing the SISU Voice Matching Test (SVMT): A novel tool for assessing voice discrimination in Chinese</t>
+          <t>Speak or shout? Nonverbal vocalizations promote rapid detection of emotions in vocal communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tianqi Xu; Xiaoming Jiang; Peng Zhang; Aijun Wang</t>
+          <t>Marc D. Pell; Haining Cui; Yondu Mori; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Behavior Research Methods, 57, 86</t>
+          <t>PLOS One</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1053,29 +1096,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.3758/s13428-025-02608-3</t>
+          <t>10.1371/journal.pone.0327529</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3758/s13428-025-02608-3</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1371/journal.pone.0327529</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Undergrad-led</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1085,17 +1129,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Semantic processing of argument structure during naturalistic story listening: Evidence from computational modeling on fMRI</t>
+          <t>Naturalistic fMRI and MEG recordings during viewing of a reality TV show</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tianqi Xu; Jixing Li; Xiaoming Jiang</t>
+          <t>Jixing Li; Qiang Wang; Yike Wang; Chengcheng Wang; Zhengwu Ma; Ruixuan Xu; Shiyan Feng; Xiaoming Jiang; Zhaoli Meng</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NeuroImage, 314, 121253</t>
+          <t>Scientific Data</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1105,24 +1149,30 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.1016/j.neuroimage.2025.121253</t>
+          <t>10.1038/s41597-025-06110-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.neuroimage.2025.121253</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1038/s41597-025-06110-5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1132,17 +1182,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Measuring the semantic priming effect across many languages</t>
+          <t>On How Vocal Cues Impact Dynamic Credibility Judgments: Mouse-Tracking Paradigm Examining Speaker Confidence and Gender Through Voice Morphing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Erin Buchanan; Kelly Cuccolo; Tom Heyman; ...; Xiaoming Jiang; ...</t>
+          <t>Zhikang Peng; Chaoyi Wang; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nature Human Behaviour, 10, 182-201</t>
+          <t>Journal of Speech, Language, and Hearing Research</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1150,21 +1200,32 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10.1044/2025_JSLHR-24-00849</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1044/2025_JSLHR-24-00849</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Multi-lab</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1174,17 +1235,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Naturalistic fMRI and MEG recordings during viewing of a reality TV show</t>
+          <t>Perceiving female physical attractiveness and expressive traits from body features and body motion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jixing Li; Qingjuan Wang; Yue Wang; Chao Wang; Zhuoran Ma; Ruoyu Xu; Shaoning Feng; Xiaoming Jiang; Zhen Meng</t>
+          <t>Lin Gao; Marc D. Pell; Zhikang Peng; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Scientific Data, 1809</t>
+          <t>BMC Psychology</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1194,24 +1255,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.1038/s41597-025-06110-5</t>
+          <t>10.1186/s40359-025-03522-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-025-06110-5</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1186/s40359-025-03522-1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1221,34 +1288,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neural evidence for encoding communicative functions in speech across linguistic forms with varying iconicity</t>
+          <t>Does Speech Prosody Shape Social Perception Equally for AI and Human Voices? A 16-Dimension Rating Study</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yi Li; Xiaoming Jiang</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Language, Cognition &amp; Neuroscience</t>
-        </is>
-      </c>
+          <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>preprint</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10.20944/preprints202510.1492.v1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.20944/preprints202510.1492.v1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1258,17 +1337,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>On how vocal cues impact dynamic credibility judgments: Mouse-tracking paradigm examining speaker confidence and gender through voice morphing</t>
+          <t>Semantic processing of argument structure during naturalistic story listening: Evidence from computational modeling on fMRI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zhikang Peng; Chao Wang; Xiaoming Jiang</t>
+          <t>Tianze Xu; Jixing Li; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Journal of Speech, Language, and Hearing Research, 68, 5261-5277</t>
+          <t>NeuroImage</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1278,24 +1357,30 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.1044/2025_JSLHR-24-00849</t>
+          <t>10.1016/j.neuroimage.2025.121253</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1044/2025_JSLHR-24-00849</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuroimage.2025.121253</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1305,17 +1390,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Perceiving female physical attractiveness and expressive traits from body features and body motion</t>
+          <t>From Theoretical Framework to Empirical Investigation: A Bibliometric Analysis of Research Evolution and Emerging Trends in Polarity Sensitivity Studies Between 1980 and 2023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lina Gao; Marc D. Pell; Zhikang Peng; Xiaoming Jiang</t>
+          <t>Lingda Kong; Yi Li; Yanting Sun; Yong Jiang; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BMC Psychology, 13, 1206</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1325,24 +1410,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.1186/s40359-025-03522-1</t>
+          <t>10.3390/languages10060119</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40359-025-03522-1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3390/languages10060119</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1352,17 +1443,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Detecting implicit biases of large language models with Bayesian hypothesis testing</t>
+          <t>Introducing the Sisu Voice Matching Test (SVMT): A novel tool for assessing voice discrimination in Chinese</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shijing Si; Xiaoming Jiang; Qing Su; Lawrence Carin</t>
+          <t>Tianze Xu; Xiaoming Jiang; Peng Zhang; Anni Wang</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Scientific Reports, 15, 12415</t>
+          <t>Behavior Research Methods</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,36 +1461,52 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10.3758/s13428-025-02608-3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3758/s13428-025-02608-3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tactile and interpersonal sound symbolic associations in patients with multiple somatic symptoms</t>
+          <t>Acoustic encoding of vocally expressed confidence and doubt in Chinese bidialectics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yi Li; Xiaobing Ma; Xiaoming Jiang; Qiang Feng; Lina Wang</t>
+          <t>Shiyan Feng; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scientific Reports, 15, 18303</t>
+          <t>The Journal of the Acoustical Society of America</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1407,16 +1514,32 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10.1121/10.0032400</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1121/10.0032400</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1426,17 +1549,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Memorization-Based Training and Testing Paradigm for Robust Vocal Identity Recognition in Expressive Speech Using Event-Related Potentials Analysis</t>
+          <t>Tracking dynamic social impressions from multidimensional voice representation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chen, W.; Jiang, X.</t>
+          <t>Xiaoming Jiang; Marc D. Pell</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
+          <t>Trends in Cognitive Sciences</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1446,29 +1569,30 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.3791/66913</t>
+          <t>10.1016/j.tics.2024.08.005</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3791/66913</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>https://www.jove.com/v/66913</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.tics.2024.08.005</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1478,54 +1602,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inconsistent prosodies more severely impair speaker discrimination of artificial-intelligence-cloned than human talkers</t>
+          <t>Exploring Pragmatic Factors on the Logical Relationships of Conditional Reasoning: A Study of Counterfactual and Hypothetical Conditionals</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Xiaoming Jiang; Jingyi Ge; Shuwan Shan; Siyuan Zou; Yiyang Ding</t>
+          <t>Lingda Kong; Yanting Sun; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Speech Prosody 2024</t>
+          <t>Behavioral Sciences</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>conference-paper</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.21437/speechprosody.2024-171</t>
+          <t>10.3390/bs14080686</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21437/speechprosody.2024-171</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.isca-archive.org/speechprosody_2024/chen24c_speechprosody.pdf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>conference</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3390/bs14080686</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Leiden, Netherlands</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1535,17 +1655,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The change in aesthetic experience and empathic concern predicts theory of mind ability: Evidence from drama improvisation training</t>
+          <t>Sound symbolic associations: evidence from visual, tactile, and interpersonal iconic perception of Mandarin rimes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hu, Y.; Li, R.; Jiang, X.; Chen, W.</t>
+          <t>Yi Li; Xiaoming Jiang</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arts in Psychotherapy</t>
+          <t>Humanities and Social Sciences Communications</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1555,24 +1675,30 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.1016/j.aip.2024.102167</t>
+          <t>10.1057/s41599-024-03502-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.aip.2024.102167</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1057/s41599-024-03502-7</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1582,17 +1708,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tracking dynamic social impressions from multidimensional voice representation</t>
+          <t>Adapting to Changes in Communication: The Orbitofrontal Cortex in Language and Speech Processing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Xiaoming Jiang; Marc D. Pell</t>
+          <t>Jiang, X.; Ma, X.; Sanford, R.; Li, X.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Trends in Cognitive Sciences, 28, 878-880</t>
+          <t>Brain Sciences</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1602,24 +1728,30 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.1016/j.tics.2024.08.005</t>
+          <t>10.3390/brainsci14030264</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.tics.2024.08.005</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3390/brainsci14030264</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1629,17 +1761,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adapting to changes in communication: The orbitofrontal cortex in language and speech processing</t>
+          <t>Auditory Challenges and Listening Effort in School-Age Children With Autism: Insights From Pupillary Dynamics During Speech-in-Noise Perception</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Xiaoming Jiang; Xiaobing Ma; Ryan Sanford; Xiaohong Li</t>
+          <t>Xu, S.; Zhang, H.; Fan, J.; Jiang, X.; Zhang, M.; Guan, J.; Ding, H.; Zhang, Y.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brain Sciences, 14, 264</t>
+          <t>Journal of Speech, Language, and Hearing Research</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1649,24 +1781,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.3390/brainsci14030264</t>
+          <t>10.1044/2024_JSLHR-23-00553</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/brainsci14030264</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1044/2024_JSLHR-23-00553</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1676,17 +1814,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acoustic encoding of vocally-expressed confidence and doubt in Chinese bidialectics</t>
+          <t>Memorization-Based Training and Testing Paradigm for Robust Vocal Identity Recognition in Expressive Speech Using Event-Related Potentials Analysis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shaoning Feng; Xiaoming Jiang</t>
+          <t>Chen, W.; Jiang, X.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Journal of the Acoustical Society of America, 156, 2860-2876</t>
+          <t>Journal of visualized experiments : JoVE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1694,16 +1832,32 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10.3791/66913</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3791/66913</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1713,17 +1867,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>眶额叶皮质在语言神经认知处理中的机制探析</t>
+          <t>The change in aesthetic experience and empathic concern predicts theory of mind ability: Evidence from drama improvisation training</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>蒋晓鸣</t>
+          <t>Hu, Y.; Li, R.; Jiang, X.; Chen, W.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>天津外国语大学学报, 31, 11-28</t>
+          <t>Arts in Psychotherapy</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1731,120 +1885,154 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10.1016/j.aip.2024.102167</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.aip.2024.102167</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>面向协作知识建构的《神经语言学》线上与线下混合式教材设计与开发实践研究</t>
+          <t>Voice-Cloning Artificial-Intelligence Speakers Can Also Mimic Human-Specific Vocal Expression</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>蒋晓鸣; 金慧</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>外语教材研究, 3(1), 1-19</t>
-        </is>
-      </c>
+          <t>Wenjun Chen; Xiaoming Jiang</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+          <t>preprint</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10.20944/preprints202312.0807.v1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.20944/preprints202312.0807.v1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>教材建设</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>语音象似性视角下状貌词的意义编码与解码：问题、模型与展望</t>
+          <t>Hearing Assistive Technology Facilitates Sentence-in-Noise Recognition in Children with Autism Spectrum Disorder</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>李怡; 蒋晓鸣</t>
+          <t>Suyun Xu; Juan Fan; Hua Zhang; Minyue Zhang; Hang Zhao; Xiaoming Jiang; Hongwei Ding; Yang Zhang</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>外国语, 47, 43-56</t>
+          <t>Journal of Speech, Language, and Hearing Research</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+          <t>preprint</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10.20944/preprints202303.0517.v1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.20944/preprints202303.0517.v1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>嗓音模仿认知神经加工的多阶段模型</t>
+          <t>Affective prosody guides facial emotion processing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>胡砚冰; 蒋晓鸣</t>
+          <t>Cui, X.; Jiang, X.; Ding, H.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>心理科学进展, 32, 499-513</t>
+          <t>Current Psychology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1852,21 +2040,32 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10.1007/s12144-022-03528-7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s12144-022-03528-7</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1876,49 +2075,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Voice-Cloning Artificial-Intelligence Speakers Can Also Mimic Human-Specific Vocal Expression</t>
+          <t>Attentional Relevance Modulates Nonverbal Attractiveness Perception in Multimodal Display</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Xiaoming Jiang</t>
+          <t>Hu, Y.; Mou, Z.; Jiang, X.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Journal of Nonverbal Behavior</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10.20944/preprints202312.0807.v1</t>
+          <t>10.1007/s10919-023-00428-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.20944/preprints202312.0807.v1</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://www.preprints.org/frontend/manuscript/f63d112d03549a13ef1f1e1e9b678621/download_pub</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://osf.io/3c7rd/overview?view_only=a194fd9070ad4ca18b2eb7d5c4d303f4</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>preprint</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1007/s10919-023-00428-7</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1928,17 +2128,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>社会心理语言学视域下言者个体与群体身份的编码和解码 / Encoding and decoding mechanisms for speakers' individual and group identities</t>
+          <t>Editorial: Psychological and neurocognitive mechanisms of presupposition processing in speech and language processing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wenjun Chen; Yanbing Hu; Xiaoming Jiang</t>
+          <t>Zhou, X.; Jiang, X.; Tan, Y.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>外国语 / Journal of Foreign Languages, 46, 68-81</t>
+          <t>Frontiers in Psychology</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1946,31 +2146,32 @@
           <t>journal-article</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10.3389/fpsyg.2023.1289045</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://jfl.shisu.edu.cn/cn/article/id/729?viewType=HTML</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://jfl.shisu.edu.cn/cn/article/pdf/preview/729.pdf</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fpsyg.2023.1289045</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1980,17 +2181,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Temporal shift length and antecedent occurrence likelihood modulate counterfactual conditional comprehension: Evidence from event-related potentials</t>
+          <t>On the scope of presupposition in discourse reading comprehension</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liwen Kong; Yu Jiang; Yan Huang; Xiaoming Jiang</t>
+          <t>Yang, Q.; Jiang, X.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brain Sciences, 13, 1724</t>
+          <t>Acta Psychologica</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2000,24 +2201,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.3390/brainsci13121724</t>
+          <t>10.1016/j.actpsy.2023.103955</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/brainsci13121724</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.actpsy.2023.103955</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2027,17 +2234,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Attentional relevance modulates nonverbal attractiveness perception in multimodal display</t>
+          <t>Temporal Shift Length and Antecedent Occurrence Likelihood Modulate Counterfactual Conditional Comprehension: Evidence from Event-Related Potentials</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yanbing Hu; Zhanao Mou; Xiaoming Jiang</t>
+          <t>Kong, L.; Jiang, Y.; Huang, Y.; Jiang, X.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Journal of Nonverbal Behavior, 47, 285-319</t>
+          <t>Brain Sciences</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2047,24 +2254,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10.1007/s10919-023-00428-7</t>
+          <t>10.3390/brainsci13121724</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s10919-023-00428-7</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3390/brainsci13121724</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2074,17 +2287,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"信"以传信，"疑"以传疑？基于人声线索的可信度编码与解码</t>
+          <t>The Psychological Science Accelerator’s COVID-19 rapid-response dataset</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>胡砚冰; 蒋晓鸣</t>
+          <t>Buchanan, E.M.; Lewis, S.C.; Paris, B.; Forscher, P.S.; Pavlacic, J.M.; Beshears, J.E.; Drexler, S.M.; Gourdon-Kanhukamwe, A.; Mallik, P.R.; Silan, M.A.A.; Miller, J.K.; IJzerman, H.; Moshontz, H.; Beaudry, J.L.; Suchow, J.W.; Chartier, C.R.; Coles, N.A.; Sharifian, M.H.; Todsen, A.L.; Levitan, C.A.; Azevedo, F.; Legate, N.; Heller, B.; Rothman, A.J.; Dorison, C.A.; Gill, B.P.; Wang, K.; Rees, V.W.; Gibbs, N.; Goldenberg, A.; Thi Nguyen, T.-V.; Gross, J.J.; Kaminski, G.; von Bastian, C.C.; Paruzel-Czachura, M.; Mosannenzadeh, F.; Azouaghe, S.; Bran, A.; Ruiz-Fernandez, S.; Santos, A.C.; Reggev, N.; Zickfeld, J.H.; Akkas, H.; Pantazi, M.; Ropovik, I.; Korbmacher, M.; Arriaga, P.; Gjoneska, B.; Warmelink, L.; Alves, S.G.; de Holanda Coelho, G.L.; Stieger, S.; Schei, V.; Hanel, P.H.P.; Szaszi, B.; Fedotov, M.; Antfolk, J.; Marcu, G.-M.; Schrötter, J.; Kunst, J.R.; Geiger, S.J.; Adetula, A.; Kocalar, H.E.; Kielińska, J.; Kačmár, P.; Bokkour, A.; Galindo-Caballero, O.J.; Djamai, I.; Pöntinen, S.J.; Agesin, B.E.; Jernsäther, T.; Urooj, A.; Rachev, N.R.; Koptjevskaja-Tamm, M.; Kurfalı, M.; Pit, I.L.; Li, R.; Çoksan, S.; Dubrov, D.; Paltrow, T.E.; Baník, G.; Korobova, T.; Studzinska, A.; Jiang, X.; Aruta, J.J.B.R.; Vintr, J.; Chiu, F.; Kaliska, L.; Berkessel, J.B.; Tümer, M.; Morales-Izquierdo, S.; Chuan-Peng, H.; Vezirian, K.; Rosa, A.D.; Bialobrzeska, O.; Vasilev, M.R.; Beitner, J.; Kácha, O.; Žuro, B.; Westerlund, M.; Nedelcheva-Datsova, M.; Findor, A.; Krupić, D.; Kowal, M.; Askelund, A.D.; Pourafshari, R.; Đorđević, J.M.; Schmidt, N.-D.; Baklanova, E.; Szala, A.; Zakharov, I.; Vranka, M.A.; Ihaya, K.; Grano, C.; Cellini, N.; Białek, M.; Anton-Boicuk, L.; Dalgar, I.; Adıgüzel, A.; Verharen, J.P.H.; Maturan, P.L.G.; Kassianos, A.P.; Oliveira, R.; Čadek, M.; Adoric, V.C.; Özdoğru, A.A.; Sverdrup, T.E.; Aczel, B.; Zambrano, D.; Ahmed, A.; Tamnes, C.K.; Yamada, Y.; Volz, L.; Sunami, N.; Suter, L.; Vieira, L.; Groyecka-Bernard, A.; Kamburidis, J.A.; Reips, U.-D.; Harutyunyan, M.; Adetula, G.A.; Allred, T.B.; Barzykowski, K.; Antazo, B.G.; Zsido, A.N.; Šakan, D.D.; Cyrus-Lai, W.; Ahlgren, L.P.; Hruška, M.; Vega, D.; Manunta, E.; Mokady, A.; Capizzi, M.; Martončik, M.; Say, N.; Filip, K.; Vilar, R.; Staniaszek, K.; Vdovic, M.; Adamkovic, M.; Johannes, N.; Hajdu, N.; Cohen, N.; Overkott, C.; Krupić, D.; Hubena, B.; Nilsonne, G.; Mioni, G.; Solorzano, C.S.; Ishii, T.; Chen, Z.; Kushnir, E.; Karaarslan, C.; Ribeiro, R.R.; Khaoudi, A.; Kossowska, M.; Bavolar, J.; Hoyer, K.; Roczniewska, M.; Karababa, A.; Becker, M.; Monteiro, R.P.; Kunisato, Y.; Metin-Orta, I.; Adamus, S.; Kozma, L.; Czarnek, G.; Domurat, A.; Štrukelj, E.; Alvarez, D.S.; Parzuchowski, M.; Massoni, S.; Czamanski-Cohen, J.; Pronizius, E.; Muchembled, F.; van Schie, K.; Saçaklı, A.; Hristova, E.; Kuzminska, A.O.; Charyate, A.; Bijlstra, G.; Afhami, R.; Majeed, N.M.; Musser, E.D.; Sirota, M.; Ross, R.M.; Yeung, S.K.; Papadatou-Pastou, M.; Foroni, F.; Almeida, I.A.T.; Grigoryev, D.; Lewis, D.M.G.; Holford, D.L.; Janssen, S.M.J.; Tatachari, S.; Batres, C.; Olofsson, J.K.; Daches, S.; Belaus, A.; Pfuhl, G.; Corral-Frias, N.S.; Sousa, D.; Röer, J.P.; Isager, P.M.; Godbersen, H.; Walczak, R.B.; Van Doren, N.; Ren, D.; Gill, T.; Voracek, M.; DeBruine, L.M.; Anne, M.; Očovaj, S.B.; Thomas, A.G.; Arvanitis, A.; Ostermann, T.; Wolfe, K.; Arinze, N.C.; Bundt, C.; Lamm, C.; Calin-Jageman, R.J.; Davis, W.E.; Karekla, M.; Zorjan, S.; Jaremka, L.M.; Uttley, J.; Hricova, M.; Koehn, M.A.; Kiselnikova, N.; Bai, H.; Krafnick, A.J.; Balci, B.B.; Ballantyne, T.; Lins, S.; Vally, Z.; Esteban-Serna, C.; Schmidt, K.; Macapagal, P.M.L.; Szwed, P.; Zdybek, P.M.; Moreau, D.; Collins, W.M.; Joy-Gaba, J.A.; Vilares, I.; Tran, U.S.; Boudesseul, J.; Albayrak-Aydemir, N.; Dixson, B.J.W.; Perillo, J.T.; Ferreira, A.; Westgate, E.C.; Aberson, C.L.; Arinze, A.I.; Jaeger, B.; Butt, M.M.; Silva, J.R.; Storage, D.S.; Janak, A.P.; Jiménez-Leal, W.; Soto, J.A.; Sorokowska, A.; McCarthy, R.; Tullett, A.M.; Frias-Armenta, M.; Ribeiro, M.F.F.; Hartanto, A.; Forbes, P.A.G.; Willis, M.L.; del Carmen Tejada R, M.; Torres, A.J.O.; Stephen, I.D.; Vaidis, D.C.; de la Rosa-Gómez, A.; Yu, K.; Sutherland, C.A.M.; Manavalan, M.; Behzadnia, B.; Urban, J.; Baskin, E.; McFall, J.P.; Ogbonnaya, C.E.; Fu, C.H.Y.; Rahal, R.-M.; Ndukaihe, I.L.G.; Hostler, T.J.; Kappes, H.B.; Sorokowski, P.; Khosla, M.; Lazarevic, L.B.; Eudave, L.; Vilsmeier, J.K.; Luis, E.O.; Muda, R.; Agadullina, E.; Cárcamo, R.A.; Reeck, C.; Anjum, G.; Venegas, M.C.T.; Misiak, M.; Ryan, R.M.; Nock, N.L.; Travaglino, G.A.; Mensink, M.C.; Feldman, G.; Wichman, A.L.; Chou, W.; Ziano, I.; Seehuus, M.; Chopik, W.J.; Kung, F.Y.H.; Carpentier, J.; Vaughn, L.A.; Du, H.; Xiao, Q.; Lima, T.J.S.; Noone, C.; Onie, S.; Verbruggen, F.; Radtke, T.; Primbs, M.A.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>心理科学, 46, 1057-1066</t>
+          <t>Scientific Data</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2092,41 +2305,52 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10.1038/s41597-022-01811-7</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41597-022-01811-7</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Segmental and suprasegmental encoding of speaker confidence in Wuxi dialect vowels</t>
+          <t>The influence of temporal information on online processing of counterfactual conditional sentences: Evidence from ERPs on temporal indicators</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yue Ji; Yanbing Hu; Xiaoming Jiang</t>
+          <t>Liao, Q.; Kong, L.; Jiang, X.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Frontiers in Psychology, 13, 1028106</t>
+          <t>Journal of Neurolinguistics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2136,44 +2360,50 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10.3389/fpsyg.2022.1028106</t>
+          <t>10.1016/j.jneuroling.2023.101143</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpsyg.2022.1028106</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.jneuroling.2023.101143</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Emotional voices modulate perception and predictions about an upcoming face</t>
+          <t>Using information of relationship closeness in the comprehension of Chinese ironic criticism: Evidence from behavioral experiments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marc D. Pell; Sameer Sethi; Simon Rigoulot; Kathrin Rothermich; Pan Liu; Xiaoming Jiang</t>
+          <t>Weng, X.; Jiang, X.; Liao, Q.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cortex, 149, 148-164</t>
+          <t>Journal of Pragmatics</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2183,44 +2413,50 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.1016/j.cortex.2021.12.017</t>
+          <t>10.1016/j.pragma.2023.07.005</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.cortex.2021.12.017</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.pragma.2023.07.005</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unattended emotional prosody affects visual processing of facial expressions in Mandarin-speaking Chinese: A comparison with English-speaking Canadians</t>
+          <t>A global experiment on motivating social distancing during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pan Liu; Simon Rigoulot; Xiaoming Jiang; Shuyi Zhang; Marc D. Pell</t>
+          <t>Legate, N.; Nguyen, T.-V.; Weinstein, N.; Moller, A.; Legault, L.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Basnight-Brown, D.M.; Ceary, C.D.; Jang, Y.; IJzerman, H.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Ryan, W.S.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Unanue, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Lerche, V.; Kovic, V.; Krizanic, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Urry, H.L.; Machin, M.A.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Moshontz, H.; Jernsäther, T.; Rahman, T.; Machin, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Von Bormann, S.M.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Primbs, M.A.; Schulenberg, S.E.; Buchanan, E.M.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Morbée, S.; Lewis, S.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Levine, S.L.; Geniole, S.N.; Akter, S.; Vracar, S.; Massoni, S.; Costa, S.; Zorjan, S.; Sarioguz, E.; Izquierdo, S.M.; Tshonda, S.S.; Miller, J.K.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Ocovaj, S.B.; Onie, S.; Lins, S.; Biberauer, T.; Çoksan, S.; Khumkom, S.; Sacakli, A.; Coles, N.A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.A.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Ryan, R.M.; Gargurevich, R.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Jai-Ai, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Wajanatinapart, P.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kacmár, P.; Macapagal, P.M.; Maniaci, M.R.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Parashar, N.; Papachristopoulos, K.; Chartier, C.R.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Mallik, P.R.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Hernandez, A.; Thogersen-Ntoumani, C.; Ntoumanis, N.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Neubauer, A.B.; Martin, N.I.; Torunsky, N.; Van Antwerpen, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Forscher, P.S.; Corral-Frías, N.S.; Ouherrou, N.; Abbas, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kurfali, M.; Kabir, M.; Muda, R.; Del Carmen M. C. Tejada Rivera, M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Arvanitis, A.; Rentzelas, P.; Vansteenkiste, M.; Metz, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Gugliandolo, M.C.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Dunn, M.R.; Korbmacher, M.; Adamkovic, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martoncik, M.; Voracek, M.; Cadek, M.; Frias-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Thomas, A.G.; Kohlová, M.B.; Paruzel-Czachura, M.; Sabristov, M.; Greenburgh, A.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Magrin, M.E.; Jones, M.V.; Li, M.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Stoyanova, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Van Hooff, M.L.M.; Varella, M.A.C.; Standage, M.; Nicolotti, M.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Lu, J.G.; Pineda, L.M.S.; Matos, L.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Smit, E.S.; Kushnir, E.; Wichman, A.L.; Ferguson, L.J.; Anton-Boicuk, L.; De Holanda Coelho, G.L.; Ahlgren, L.; Liga, F.; Levitan, C.A.; Micheli, L.; Gunton, L.-A.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Beatrix, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wylie, K.; Wachowicz, J.; Charyate, A.C.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Belaus, A.; Emmanuel Agesin, B.B.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Morris, K.; Klevjer, K.; Van Schie, K.; Vezirian, K.; Damnjanovic, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Staniaszek, K.; Adetula, A.; Grzech, K.; Hoyer, K.; Moon, K.; Khaobunmasiri, S.; Rana, K.; Janjic, K.; Suchow, J.W.; Kielinska, J.; Cruz Vásquez, J.E.; Chanal, J.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Askelund, A.D.; Pavlacic, J.M.; Benka, J.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Waterschoot, J.; Moss, J.D.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Joy-Gaba, J.A.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Djordjevic, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Groyecka-Bernard, A.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Martela, F.; Foroni, F.; Forest, J.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinova, E.; Strukelj, E.; Etebari, Z.; Bradshaw, E.L.; Baskin, E.; Garcia, E.O.L.; Musser, E.; Van Steenkiste, I.M.M.; Ahn, E.R.; Quested, E.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Sakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popovic, D.; Dunleavy, D.; Djamai, I.; Krupic, D.; Herrera, D.; Vega, D.; Du, H.; Mola, D.; Chakarova, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Boller, D.; Rosa, A.D.; Dimova, D.; Krupic, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; Von Bastian, C.C.; Sutherland, C.A.M.; Ebersole, C.R.; Overkott, C.; Aberson, C.L.; Wang, C.; Niemiec, C.P.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Brownlow, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Ferreyra, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Vermote, B.J.; Bokkour, A.; Bogatyreva, N.; Shi, J.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Bayyat, M.M.; Cocco, B.; Ahmed, A.; Chou, W.-L.; Barkoukis, V.; Hubena, B.; Khaoudi, A.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babincák, P.; Soenens, B.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Ait El Arabi, K.; Özdogru, A.A.; Rothbaum, A.O.; Torres, A.O.; Theodoropoulou, A.; Skowronek, A.; Urooj, A.; Jurkovic, A.P.; Singh, A.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Landry, A.T.; Ferreira, A.; Santos, A.C.; De La Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Luxon, A.M.; Todsen, A.L.; Karababa, A.; Janak, A.; Pilato, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Journal of Cross-Cultural Psychology, 52(3), 275-294</t>
+          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2230,81 +2466,103 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.1177/0022022121990897</t>
+          <t>10.1073/pnas.2111091119</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0022022121990897</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1073/pnas.2111091119</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Immediate on-line use of prosody reveals the ironic intentions of a speaker: Neurophysiological evidence</t>
+          <t>Common and differential acoustic representation of interpersonal and tactile iconic perception of Mandarin vowels</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maël Mauchand; Jonathan Caballero; Xiaoming Jiang; Marc D. Pell</t>
+          <t>Li, Y.; Jiang, X.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cognitive, Affective &amp; Behavioral Neuroscience, 21, 74-92</t>
+          <t>Proceedings of the Annual Conference of the International Speech Communication Association, INTERSPEECH</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>conference-paper</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10.21437/Interspeech.2022-10531</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.21437/Interspeech.2022-10531</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cortical processing of speaker politeness: Tracking the dynamic effects of voice tone and politeness markers</t>
+          <t>Emotional voices modulate perception and predictions about an upcoming face</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jonathan Caballero; Maël Mauchand; Xiaoming Jiang; Marc D. Pell</t>
+          <t>Pell, M.D.; Sethi, S.; Rigoulot, S.; Rothermich, K.; Liu, P.; Jiang, X.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Social Neuroscience, 16(4), 423-438</t>
+          <t>Cortex</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2314,44 +2572,50 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.1080/17470919.2021.1938667</t>
+          <t>10.1016/j.cortex.2021.12.017</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/17470919.2021.1938667</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.cortex.2021.12.017</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>To believe or not to believe? How voice and accent information in speech alter listener impressions of trust</t>
+          <t>Erratum: A global experiment on motivating social distancing during the COVID-19 pandemic (Proceedings of the National Academy of Sciences of the United States of America (2022) 119 (e2111091119) DOI: 10.1073/pnas.2111091119)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Xiaoming Jiang; Kira Gossack-Keenan; Marc D. Pell</t>
+          <t>Legate, N.; Nguyen, T.-V.; Weinstein, N.; Moller, A.; Legault, L.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Basnight-Brown, D.M.; Ceary, C.D.; Jang, Y.; IJzerman, H.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Ryan, W.S.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Unanue, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Lerche, V.; Kovic, V.; Krizanic, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Urry, H.L.; Machin, M.A.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Moshontz, H.; Jernsäther, T.; Rahman, T.; Machin, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Von Bormann, S.M.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Primbs, M.A.; Schulenberg, S.E.; Buchanan, E.M.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Morbée, S.; Lewis, S.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Levine, S.L.; Geniole, S.N.; Akter, S.; Vracar, S.; Massoni, S.; Costa, S.; Zorjan, S.; Sarioguz, E.; Izquierdo, S.M.; Tshonda, S.S.; Miller, J.K.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Ocovaj, S.B.; Onie, S.; Lins, S.; Biberauer, T.; Çoksan, S.; Khumkom, S.; Sacakli, A.; Coles, N.A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.A.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Ryan, R.M.; Gargurevich, R.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Jai-Ai, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Wajanatinapart, P.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kacmár, P.; Macapagal, P.M.; Maniaci, M.R.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Parashar, N.; Papachristopoulos, K.; Chartier, C.R.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Mallik, P.R.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Hernandez, A.; Thogersen-Ntoumani, C.; Ntoumanis, N.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Neubauer, A.B.; Martin, N.I.; Torunsky, N.; Van Antwerpen, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Forscher, P.S.; Corral-Frías, N.S.; Ouherrou, N.; Abbas, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kurfali, M.; Kabir, M.; Muda, R.; Del Carmen M. C. Tejada Rivera, M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Arvanitis, A.; Rentzelas, P.; Vansteenkiste, M.; Metz, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Gugliandolo, M.C.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Dunn, M.R.; Korbmacher, M.; Adamkovic, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martoncik, M.; Voracek, M.; Cadek, M.; Frias-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Thomas, A.G.; Kohlová, M.B.; Paruzel-Czachura, M.; Sabristov, M.; Greenburgh, A.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Magrin, M.E.; Jones, M.V.; Li, M.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Stoyanova, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Van Hooff, M.L.M.; Varella, M.A.C.; Standage, M.; Nicolotti, M.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Lu, J.G.; Pineda, L.M.S.; Matos, L.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Smit, E.S.; Kushnir, E.; Wichman, A.L.; Ferguson, L.J.; Anton-Boicuk, L.; De Holanda Coelho, G.L.; Ahlgren, L.; Liga, F.; Levitan, C.A.; Micheli, L.; Gunton, L.-A.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Beatrix, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wylie, K.; Wachowicz, J.; Charyate, A.C.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Belaus, A.; Emmanuel Agesin, B.B.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Morris, K.; Klevjer, K.; Van Schie, K.; Vezirian, K.; Damnjanovic, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Staniaszek, K.; Adetula, A.; Grzech, K.; Hoyer, K.; Moon, K.; Khaobunmasiri, S.; Rana, K.; Janjic, K.; Suchow, J.W.; Kielinska, J.; Cruz Vásquez, J.E.; Chanal, J.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Askelund, A.D.; Pavlacic, J.M.; Benka, J.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Waterschoot, J.; Moss, J.D.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Joy-Gaba, J.A.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Djordjevic, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Groyecka-Bernard, A.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Martela, F.; Foroni, F.; Forest, J.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinova, E.; Strukelj, E.; Etebari, Z.; Bradshaw, E.L.; Baskin, E.; Garcia, E.O.L.; Musser, E.; Van Steenkiste, I.M.M.; Ahn, E.R.; Quested, E.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Sakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popovic, D.; Dunleavy, D.; Djamai, I.; Krupic, D.; Herrera, D.; Vega, D.; Du, H.; Mola, D.; Chakarova, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Boller, D.; Rosa, A.D.; Dimova, D.; Krupic, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; Von Bastian, C.C.; Sutherland, C.A.M.; Ebersole, C.R.; Overkott, C.; Aberson, C.L.; Wang, C.; Niemiec, C.P.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Brownlow, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Ferreyra, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Vermote, B.J.; Bokkour, A.; Bogatyreva, N.; Shi, J.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Bayyat, M.M.; Cocco, B.; Ahmed, A.; Chou, W.-L.; Barkoukis, V.; Hubena, B.; Khaoudi, A.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babincák, P.; Soenens, B.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Ait El Arabi, K.; Özdogru, A.A.; Rothbaum, A.O.; Torres, A.O.; Theodoropoulou, A.; Skowronek, A.; Urooj, A.; Jurkovic, A.P.; Singh, A.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Landry, A.T.; Ferreira, A.; Santos, A.C.; De La Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Luxon, A.M.; Todsen, A.L.; Karababa, A.; Janak, A.; Pilato, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Quarterly Journal of Experimental Psychology, 73(1), 55-79</t>
+          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2361,44 +2625,50 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.1177/1747021819865833</t>
+          <t>10.1073/pnas.2213828119</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/1747021819865833</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1073/pnas.2213828119</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>文化互鉴视角下非言语表情的嗓音编码和解码</t>
+          <t>From Infant Attachment to God Belief: Rethinking Factors of Trust Underlying the Psychological Origin and Developmental Processes of Religious Belief</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>蒋晓鸣</t>
+          <t>Jiang, X.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>同济大学学报（社会科学版）, 31, 116-124</t>
+          <t>Logos and Pneuma - Chinese Journal of Theology</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2406,130 +2676,150 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
+          <t>0000-0002-5171-9774</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stereotypes vs. general knowledge: How listener-specific expectations shape the processing of counter-expectation meaning</t>
+          <t>Impacts of aging on suprasegmental and segmental encoding of vocally-expressed confidence in Wuxi dialect</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Xun Li; Xiaoming Jiang</t>
+          <t>Ji, Y.; Sun, Q.; Peng, Z.; Jiang, X.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lingua</t>
+          <t>2022 13th International Symposium on Chinese Spoken Language Processing, ISCSLP 2022</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>journal-article</t>
+          <t>conference-paper</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.1016/j.lingua.2026.104185</t>
+          <t>10.1109/ISCSLP57327.2022.10037951</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.lingua.2026.104185</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1109/ISCSLP57327.2022.10037951</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Context-dependent acoustic dimensions underlying voice discrimination: Evidence from interpretable machine learning modeling of human perception</t>
+          <t>In COVID-19 Health Messaging, Loss Framing Increases Anxiety with Little-to-No Concomitant Benefits: Experimental Evidence from 84 Countries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tianze Xu; Xiaoming Jiang; Volker Dellwo</t>
+          <t>Dorison, C.A.; Lerner, J.S.; Heller, B.H.; Rothman, A.J.; Kawachi, I.I.; Wang, K.; Rees, V.W.; Gill, B.P.; Gibbs, N.; Ebersole, C.R.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Ceary, C.D.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Križanić, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Jernsäther, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Schulenberg, S.E.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Lewis, S.C.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Geniole, S.N.; Vračar, S.; Massoni, S.; Zorjan, S.; Sarıoğuz, E.; Izquierdo, S.M.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Očovaj, S.B.; Onie, S.; Lins, S.; Çoksan, S.; Sacakli, A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kačmár, P.; Macapagal, P.M.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Papachristopoulos, K.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Torunsky, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Corral-Frías, N.S.; Ouherrou, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kabir, M.; Muda, R.; Tejada Rivera, M.C.M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Korbmacher, M.; Adamkovič, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martončik, M.; Voracek, M.; Čadek, M.; Frías-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Kohlová, M.B.; Paruzel-Czachura, M.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Jones, M.V.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Varella, M.A.C.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Pineda, L.M.S.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Kushnir, E.; Anton-Boicuk, L.; de Holanda Coelho, G.L.; Ahlgren, L.; Levitan, C.A.; Micheli, L.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wachowicz, J.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Agesin, B.E.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Klevjer, K.; van Schie, K.; Vezirian, K.; Damnjanović, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Grzech, K.; Hoyer, K.; Moon, K.; Rana, K.; Janjić, K.; Suchow, J.W.; Kielińska, J.; Cruz Vásquez, J.E.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Pavlacic, J.M.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Đorđević, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.H.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Foroni, F.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinov, E.; Štrukelj, E.; Etebari, Z.; Baskin, E.; Garcia, E.O.L.; Musser, E.; van Steenkiste, I.M.M.; Ahn, E.R.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Šakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popović, D.; Dunleavy, D.; Djamai, I.; Krupić, D.; Vega, D.; Du, H.; Mola, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Rosa, A.D.; Krupić, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; von Bastian, C.C.; Sutherland, C.A.; Overkott, C.; Aberson, C.L.; Wang, C.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Bokkour, A.; Bogatyreva, N.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Cocco, B.; Chou, W.-L.; Hubena, B.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babinčák, P.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Arabi, K.A.E.; Özdoğru, A.A.; Olaya Torres, A.J.; Theodoropoulou, A.; Jurković, A.P.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Thibault Landry, A.; Ferreira, A.; Santos, A.C.; De la Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Todsen, A.L.; Karababa, A.; Janak, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.; Urooj, A.; Khaoudi, A.; Ahmed, A.; Groyecka-Bernard, A.; Askelund, A.D.; Adetula, A.; Belaus, A.; Charyate, A.C.; Wichman, A.L.; Stoyanova, A.; Greenburgh, A.; Thomas, A.G.; Arvanitis, A.; Forscher, P.S.; Mallik, P.R.; Primbs, M.A.; Miller, J.K.; Moshontz, H.; Urry, H.L.; IJzerman, H.; Basnight-Brown, D.M.; Chartier, C.R.; Buchanan, E.M.; Coles, N.A.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Affective Science</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.31234/osf.io/4zrwy_v3</t>
+          <t>10.1007/s42761-022-00128-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://doi.org/10.31234/osf.io/4zrwy_v3</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1007/s42761-022-00128-3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>From Theoretical Framework to Empirical Investigation: A Bibliometric Analysis of Research Evolution and Emerging Trends in Polarity Sensitivity Studies Between 1980 and 2023</t>
+          <t>Increased spontaneous fronto-central oscillatory power during eye closing in patients with multiple somatic symptoms</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lingda Kong; Yi Li; Yanting Sun; Yong Jiang; Xiaoming Jiang</t>
+          <t>Ma, X.; Jiang, X.; Jiang, Y.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Psychiatry Research - Neuroimaging</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2539,44 +2829,50 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.3390/languages10060119</t>
+          <t>10.1016/j.pscychresns.2022.111489</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/languages10060119</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.pscychresns.2022.111489</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acoustic encoding of vocally expressed confidence and doubt in Chinese bidialectics</t>
+          <t>Neural segregation in left inferior frontal gyrus of semantic processes at different levels of syntactic hierarchy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shiyan Feng; Xiaoming Jiang</t>
+          <t>Li, X.; Jiang, X.; Chang, W.; Tan, Y.; Zhou, X.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>The Journal of the Acoustical Society of America</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2586,44 +2882,50 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.1121/10.0032400</t>
+          <t>10.1016/j.neuropsychologia.2022.108254</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1121/10.0032400</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2022.108254</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Exploring Pragmatic Factors on the Logical Relationships of Conditional Reasoning: A Study of Counterfactual and Hypothetical Conditionals</t>
+          <t>Resting-state occipito-frontal alpha connectome is linked to differential word learning ability in adult learners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lingda Kong; Yanting Sun; Xiaoming Jiang</t>
+          <t>Huang, Y.; Deng, Y.; Jiang, X.; Chen, Y.; Mao, T.; Xu, Y.; Jiang, C.; Rao, H.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Behavioral Sciences</t>
+          <t>Frontiers in Neuroscience</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2633,44 +2935,50 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.3390/bs14080686</t>
+          <t>10.3389/fnins.2022.953315</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/bs14080686</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fnins.2022.953315</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sound symbolic associations: evidence from visual, tactile, and interpersonal iconic perception of Mandarin rimes</t>
+          <t>Segmental and suprasegmental encoding of speaker confidence in Wuxi dialect vowels</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yi Li; Xiaoming Jiang</t>
+          <t>Ji, Y.; Hu, Y.; Jiang, X.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Humanities and Social Sciences Communications</t>
+          <t>Frontiers in Psychology</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2680,44 +2988,50 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10.1057/s41599-024-03502-7</t>
+          <t>10.3389/fpsyg.2022.1028106</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1057/s41599-024-03502-7</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fpsyg.2022.1028106</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Auditory Challenges and Listening Effort in School-Age Children With Autism: Insights From Pupillary Dynamics During Speech-in-Noise Perception</t>
+          <t>Cortical processing of speaker politeness: Tracking the dynamic effects of voice tone and politeness markers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Xu, S.; Zhang, H.; Fan, J.; Jiang, X.; Zhang, M.; Guan, J.; Ding, H.; Zhang, Y.</t>
+          <t>Caballero, J.A.; Mauchand, M.; Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Journal of Speech, Language, and Hearing Research</t>
+          <t>Social Neuroscience</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2727,91 +3041,103 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10.1044/2024_JSLHR-23-00553</t>
+          <t>10.1080/17470919.2021.1938667</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1044/2024_JSLHR-23-00553</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1080/17470919.2021.1938667</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hearing Assistive Technology Facilitates Sentence-in-Noise Recognition in Children with Autism Spectrum Disorder</t>
+          <t>Immediate online use of prosody reveals the ironic intentions of a speaker: neurophysiological evidence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Suyun Xu; Juan Fan; Hua Zhang; Minyue Zhang; Hang Zhao; Xiaoming Jiang; Hongwei Ding; Yang Zhang</t>
+          <t>Mauchand, M.; Caballero, J.A.; Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Journal of Speech, Language, and Hearing Research</t>
+          <t>Cognitive, Affective and Behavioral Neuroscience</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.20944/preprints202303.0517.v1</t>
+          <t>10.3758/s13415-020-00849-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://doi.org/10.20944/preprints202303.0517.v1</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3758/s13415-020-00849-7</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Affective prosody guides facial emotion processing</t>
+          <t>Unattended Emotional Prosody Affects Visual Processing of Facial Expressions in Mandarin-Speaking Chinese: A Comparison With English-Speaking Canadians</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cui, X.; Jiang, X.; Ding, H.</t>
+          <t>Liu, P.; Rigoulot, S.; Jiang, X.; Zhang, S.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Current Psychology</t>
+          <t>Journal of Cross-Cultural Psychology</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2821,44 +3147,46 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.1007/s12144-022-03528-7</t>
+          <t>10.1177/0022022121990897</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s12144-022-03528-7</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1177/0022022121990897</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Editorial: Psychological and neurocognitive mechanisms of presupposition processing in speech and language processing</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Zhou, X.; Jiang, X.; Tan, Y.</t>
-        </is>
-      </c>
+          <t>An alternative structure rescues failed semantics? Strong global expectancy reduces local-mismatch N400 in Chinese flexible structures</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Frontiers in Psychology</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2868,44 +3196,50 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.3389/fpsyg.2023.1289045</t>
+          <t>10.1016/j.neuropsychologia.2020.107380</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpsyg.2023.1289045</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2020.107380</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>On the scope of presupposition in discourse reading comprehension</t>
+          <t>Gender interference in processing Chinese compound reflexive: evidence from reading eye-tracking</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yang, Q.; Jiang, X.</t>
+          <t>Chang, W.; Duan, Y.; Qian, J.; Wu, F.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Acta Psychologica</t>
+          <t>Language, Cognition and Neuroscience</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2915,44 +3249,50 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10.1016/j.actpsy.2023.103955</t>
+          <t>10.1080/23273798.2020.1781213</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.actpsy.2023.103955</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1080/23273798.2020.1781213</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Psychological Science Accelerator’s COVID-19 rapid-response dataset</t>
+          <t>Neural responses to interpersonal requests: Effects of imposition and vocally-expressed stance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Buchanan, E.M.; Lewis, S.C.; Paris, B.; Forscher, P.S.; Pavlacic, J.M.; Beshears, J.E.; Drexler, S.M.; Gourdon-Kanhukamwe, A.; Mallik, P.R.; Silan, M.A.A.; Miller, J.K.; IJzerman, H.; Moshontz, H.; Beaudry, J.L.; Suchow, J.W.; Chartier, C.R.; Coles, N.A.; Sharifian, M.H.; Todsen, A.L.; Levitan, C.A.; Azevedo, F.; Legate, N.; Heller, B.; Rothman, A.J.; Dorison, C.A.; Gill, B.P.; Wang, K.; Rees, V.W.; Gibbs, N.; Goldenberg, A.; Thi Nguyen, T.-V.; Gross, J.J.; Kaminski, G.; von Bastian, C.C.; Paruzel-Czachura, M.; Mosannenzadeh, F.; Azouaghe, S.; Bran, A.; Ruiz-Fernandez, S.; Santos, A.C.; Reggev, N.; Zickfeld, J.H.; Akkas, H.; Pantazi, M.; Ropovik, I.; Korbmacher, M.; Arriaga, P.; Gjoneska, B.; Warmelink, L.; Alves, S.G.; de Holanda Coelho, G.L.; Stieger, S.; Schei, V.; Hanel, P.H.P.; Szaszi, B.; Fedotov, M.; Antfolk, J.; Marcu, G.-M.; Schrötter, J.; Kunst, J.R.; Geiger, S.J.; Adetula, A.; Kocalar, H.E.; Kielińska, J.; Kačmár, P.; Bokkour, A.; Galindo-Caballero, O.J.; Djamai, I.; Pöntinen, S.J.; Agesin, B.E.; Jernsäther, T.; Urooj, A.; Rachev, N.R.; Koptjevskaja-Tamm, M.; Kurfalı, M.; Pit, I.L.; Li, R.; Çoksan, S.; Dubrov, D.; Paltrow, T.E.; Baník, G.; Korobova, T.; Studzinska, A.; Jiang, X.; Aruta, J.J.B.R.; Vintr, J.; Chiu, F.; Kaliska, L.; Berkessel, J.B.; Tümer, M.; Morales-Izquierdo, S.; Chuan-Peng, H.; Vezirian, K.; Rosa, A.D.; Bialobrzeska, O.; Vasilev, M.R.; Beitner, J.; Kácha, O.; Žuro, B.; Westerlund, M.; Nedelcheva-Datsova, M.; Findor, A.; Krupić, D.; Kowal, M.; Askelund, A.D.; Pourafshari, R.; Đorđević, J.M.; Schmidt, N.-D.; Baklanova, E.; Szala, A.; Zakharov, I.; Vranka, M.A.; Ihaya, K.; Grano, C.; Cellini, N.; Białek, M.; Anton-Boicuk, L.; Dalgar, I.; Adıgüzel, A.; Verharen, J.P.H.; Maturan, P.L.G.; Kassianos, A.P.; Oliveira, R.; Čadek, M.; Adoric, V.C.; Özdoğru, A.A.; Sverdrup, T.E.; Aczel, B.; Zambrano, D.; Ahmed, A.; Tamnes, C.K.; Yamada, Y.; Volz, L.; Sunami, N.; Suter, L.; Vieira, L.; Groyecka-Bernard, A.; Kamburidis, J.A.; Reips, U.-D.; Harutyunyan, M.; Adetula, G.A.; Allred, T.B.; Barzykowski, K.; Antazo, B.G.; Zsido, A.N.; Šakan, D.D.; Cyrus-Lai, W.; Ahlgren, L.P.; Hruška, M.; Vega, D.; Manunta, E.; Mokady, A.; Capizzi, M.; Martončik, M.; Say, N.; Filip, K.; Vilar, R.; Staniaszek, K.; Vdovic, M.; Adamkovic, M.; Johannes, N.; Hajdu, N.; Cohen, N.; Overkott, C.; Krupić, D.; Hubena, B.; Nilsonne, G.; Mioni, G.; Solorzano, C.S.; Ishii, T.; Chen, Z.; Kushnir, E.; Karaarslan, C.; Ribeiro, R.R.; Khaoudi, A.; Kossowska, M.; Bavolar, J.; Hoyer, K.; Roczniewska, M.; Karababa, A.; Becker, M.; Monteiro, R.P.; Kunisato, Y.; Metin-Orta, I.; Adamus, S.; Kozma, L.; Czarnek, G.; Domurat, A.; Štrukelj, E.; Alvarez, D.S.; Parzuchowski, M.; Massoni, S.; Czamanski-Cohen, J.; Pronizius, E.; Muchembled, F.; van Schie, K.; Saçaklı, A.; Hristova, E.; Kuzminska, A.O.; Charyate, A.; Bijlstra, G.; Afhami, R.; Majeed, N.M.; Musser, E.D.; Sirota, M.; Ross, R.M.; Yeung, S.K.; Papadatou-Pastou, M.; Foroni, F.; Almeida, I.A.T.; Grigoryev, D.; Lewis, D.M.G.; Holford, D.L.; Janssen, S.M.J.; Tatachari, S.; Batres, C.; Olofsson, J.K.; Daches, S.; Belaus, A.; Pfuhl, G.; Corral-Frias, N.S.; Sousa, D.; Röer, J.P.; Isager, P.M.; Godbersen, H.; Walczak, R.B.; Van Doren, N.; Ren, D.; Gill, T.; Voracek, M.; DeBruine, L.M.; Anne, M.; Očovaj, S.B.; Thomas, A.G.; Arvanitis, A.; Ostermann, T.; Wolfe, K.; Arinze, N.C.; Bundt, C.; Lamm, C.; Calin-Jageman, R.J.; Davis, W.E.; Karekla, M.; Zorjan, S.; Jaremka, L.M.; Uttley, J.; Hricova, M.; Koehn, M.A.; Kiselnikova, N.; Bai, H.; Krafnick, A.J.; Balci, B.B.; Ballantyne, T.; Lins, S.; Vally, Z.; Esteban-Serna, C.; Schmidt, K.; Macapagal, P.M.L.; Szwed, P.; Zdybek, P.M.; Moreau, D.; Collins, W.M.; Joy-Gaba, J.A.; Vilares, I.; Tran, U.S.; Boudesseul, J.; Albayrak-Aydemir, N.; Dixson, B.J.W.; Perillo, J.T.; Ferreira, A.; Westgate, E.C.; Aberson, C.L.; Arinze, A.I.; Jaeger, B.; Butt, M.M.; Silva, J.R.; Storage, D.S.; Janak, A.P.; Jiménez-Leal, W.; Soto, J.A.; Sorokowska, A.; McCarthy, R.; Tullett, A.M.; Frias-Armenta, M.; Ribeiro, M.F.F.; Hartanto, A.; Forbes, P.A.G.; Willis, M.L.; del Carmen Tejada R, M.; Torres, A.J.O.; Stephen, I.D.; Vaidis, D.C.; de la Rosa-Gómez, A.; Yu, K.; Sutherland, C.A.M.; Manavalan, M.; Behzadnia, B.; Urban, J.; Baskin, E.; McFall, J.P.; Ogbonnaya, C.E.; Fu, C.H.Y.; Rahal, R.-M.; Ndukaihe, I.L.G.; Hostler, T.J.; Kappes, H.B.; Sorokowski, P.; Khosla, M.; Lazarevic, L.B.; Eudave, L.; Vilsmeier, J.K.; Luis, E.O.; Muda, R.; Agadullina, E.; Cárcamo, R.A.; Reeck, C.; Anjum, G.; Venegas, M.C.T.; Misiak, M.; Ryan, R.M.; Nock, N.L.; Travaglino, G.A.; Mensink, M.C.; Feldman, G.; Wichman, A.L.; Chou, W.; Ziano, I.; Seehuus, M.; Chopik, W.J.; Kung, F.Y.H.; Carpentier, J.; Vaughn, L.A.; Du, H.; Xiao, Q.; Lima, T.J.S.; Noone, C.; Onie, S.; Verbruggen, F.; Radtke, T.; Primbs, M.A.</t>
+          <t>Vergis, N.; Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Scientific Data</t>
+          <t>Brain Research</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2962,44 +3302,50 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10.1038/s41597-022-01811-7</t>
+          <t>10.1016/j.brainres.2020.146855</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41597-022-01811-7</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.brainres.2020.146855</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The influence of temporal information on online processing of counterfactual conditional sentences: Evidence from ERPs on temporal indicators</t>
+          <t>Neurophysiological correlates of sexually evocative speech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liao, Q.; Kong, L.; Jiang, X.</t>
+          <t>Rigoulot, S.; Jiang, X.; Vergis, N.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Journal of Neurolinguistics</t>
+          <t>Biological Psychology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3009,44 +3355,50 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.1016/j.jneuroling.2023.101143</t>
+          <t>10.1016/j.biopsycho.2020.107909</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jneuroling.2023.101143</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.biopsycho.2020.107909</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Using information of relationship closeness in the comprehension of Chinese ironic criticism: Evidence from behavioral experiments</t>
+          <t>To believe or not to believe? How voice and accent information in speech alter listener impressions of trust</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Weng, X.; Jiang, X.; Liao, Q.</t>
+          <t>Jiang, X.; Gossack-Keenan, K.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Journal of Pragmatics</t>
+          <t>Quarterly Journal of Experimental Psychology</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3056,44 +3408,46 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10.1016/j.pragma.2023.07.005</t>
+          <t>10.1177/1747021819865833</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pragma.2023.07.005</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1177/1747021819865833</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A global experiment on motivating social distancing during the COVID-19 pandemic</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Legate, N.; Nguyen, T.-V.; Weinstein, N.; Moller, A.; Legault, L.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Basnight-Brown, D.M.; Ceary, C.D.; Jang, Y.; IJzerman, H.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Ryan, W.S.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Unanue, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Lerche, V.; Kovic, V.; Krizanic, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Urry, H.L.; Machin, M.A.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Moshontz, H.; Jernsäther, T.; Rahman, T.; Machin, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Von Bormann, S.M.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Primbs, M.A.; Schulenberg, S.E.; Buchanan, E.M.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Morbée, S.; Lewis, S.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Levine, S.L.; Geniole, S.N.; Akter, S.; Vracar, S.; Massoni, S.; Costa, S.; Zorjan, S.; Sarioguz, E.; Izquierdo, S.M.; Tshonda, S.S.; Miller, J.K.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Ocovaj, S.B.; Onie, S.; Lins, S.; Biberauer, T.; Çoksan, S.; Khumkom, S.; Sacakli, A.; Coles, N.A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.A.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Ryan, R.M.; Gargurevich, R.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Jai-Ai, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Wajanatinapart, P.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kacmár, P.; Macapagal, P.M.; Maniaci, M.R.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Parashar, N.; Papachristopoulos, K.; Chartier, C.R.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Mallik, P.R.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Hernandez, A.; Thogersen-Ntoumani, C.; Ntoumanis, N.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Neubauer, A.B.; Martin, N.I.; Torunsky, N.; Van Antwerpen, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Forscher, P.S.; Corral-Frías, N.S.; Ouherrou, N.; Abbas, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kurfali, M.; Kabir, M.; Muda, R.; Del Carmen M. C. Tejada Rivera, M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Arvanitis, A.; Rentzelas, P.; Vansteenkiste, M.; Metz, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Gugliandolo, M.C.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Dunn, M.R.; Korbmacher, M.; Adamkovic, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martoncik, M.; Voracek, M.; Cadek, M.; Frias-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Thomas, A.G.; Kohlová, M.B.; Paruzel-Czachura, M.; Sabristov, M.; Greenburgh, A.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Magrin, M.E.; Jones, M.V.; Li, M.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Stoyanova, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Van Hooff, M.L.M.; Varella, M.A.C.; Standage, M.; Nicolotti, M.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Lu, J.G.; Pineda, L.M.S.; Matos, L.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Smit, E.S.; Kushnir, E.; Wichman, A.L.; Ferguson, L.J.; Anton-Boicuk, L.; De Holanda Coelho, G.L.; Ahlgren, L.; Liga, F.; Levitan, C.A.; Micheli, L.; Gunton, L.-A.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Beatrix, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wylie, K.; Wachowicz, J.; Charyate, A.C.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Belaus, A.; Emmanuel Agesin, B.B.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Morris, K.; Klevjer, K.; Van Schie, K.; Vezirian, K.; Damnjanovic, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Staniaszek, K.; Adetula, A.; Grzech, K.; Hoyer, K.; Moon, K.; Khaobunmasiri, S.; Rana, K.; Janjic, K.; Suchow, J.W.; Kielinska, J.; Cruz Vásquez, J.E.; Chanal, J.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Askelund, A.D.; Pavlacic, J.M.; Benka, J.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Waterschoot, J.; Moss, J.D.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Joy-Gaba, J.A.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Djordjevic, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Groyecka-Bernard, A.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Martela, F.; Foroni, F.; Forest, J.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinova, E.; Strukelj, E.; Etebari, Z.; Bradshaw, E.L.; Baskin, E.; Garcia, E.O.L.; Musser, E.; Van Steenkiste, I.M.M.; Ahn, E.R.; Quested, E.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Sakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popovic, D.; Dunleavy, D.; Djamai, I.; Krupic, D.; Herrera, D.; Vega, D.; Du, H.; Mola, D.; Chakarova, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Boller, D.; Rosa, A.D.; Dimova, D.; Krupic, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; Von Bastian, C.C.; Sutherland, C.A.M.; Ebersole, C.R.; Overkott, C.; Aberson, C.L.; Wang, C.; Niemiec, C.P.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Brownlow, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Ferreyra, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Vermote, B.J.; Bokkour, A.; Bogatyreva, N.; Shi, J.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Bayyat, M.M.; Cocco, B.; Ahmed, A.; Chou, W.-L.; Barkoukis, V.; Hubena, B.; Khaoudi, A.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babincák, P.; Soenens, B.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Ait El Arabi, K.; Özdogru, A.A.; Rothbaum, A.O.; Torres, A.O.; Theodoropoulou, A.; Skowronek, A.; Urooj, A.; Jurkovic, A.P.; Singh, A.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Landry, A.T.; Ferreira, A.; Santos, A.C.; De La Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Luxon, A.M.; Todsen, A.L.; Karababa, A.; Janak, A.; Pilato, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.</t>
-        </is>
-      </c>
+          <t>Eye Movements Reveal Delayed Use of Construction-Based Pragmatic Information During Online Sentence Reading: A Case of Chinese Lian…dou Construction</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+          <t>Frontiers in Psychology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3103,222 +3457,254 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10.1073/pnas.2111091119</t>
+          <t>10.3389/fpsyg.2019.02211</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1073/pnas.2111091119</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fpsyg.2019.02211</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Common and differential acoustic representation of interpersonal and tactile iconic perception of Mandarin vowels</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Li, Y.; Jiang, X.</t>
-        </is>
-      </c>
+          <t>Commentary: A Neural Mechanism of Social Categorization</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Proceedings of the Annual Conference of the International Speech Communication Association, INTERSPEECH</t>
+          <t>Frontiers in Neuroscience</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>conference-paper</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10.21437/Interspeech.2022-10531</t>
+          <t>10.3389/fnins.2019.00368</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21437/Interspeech.2022-10531</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fnins.2019.00368</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Erratum: A global experiment on motivating social distancing during the COVID-19 pandemic (Proceedings of the National Academy of Sciences of the United States of America (2022) 119 (e2111091119) DOI: 10.1073/pnas.2111091119)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Legate, N.; Nguyen, T.-V.; Weinstein, N.; Moller, A.; Legault, L.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Basnight-Brown, D.M.; Ceary, C.D.; Jang, Y.; IJzerman, H.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Ryan, W.S.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Unanue, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Lerche, V.; Kovic, V.; Krizanic, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Urry, H.L.; Machin, M.A.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Moshontz, H.; Jernsäther, T.; Rahman, T.; Machin, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Von Bormann, S.M.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Primbs, M.A.; Schulenberg, S.E.; Buchanan, E.M.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Morbée, S.; Lewis, S.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Levine, S.L.; Geniole, S.N.; Akter, S.; Vracar, S.; Massoni, S.; Costa, S.; Zorjan, S.; Sarioguz, E.; Izquierdo, S.M.; Tshonda, S.S.; Miller, J.K.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Ocovaj, S.B.; Onie, S.; Lins, S.; Biberauer, T.; Çoksan, S.; Khumkom, S.; Sacakli, A.; Coles, N.A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.A.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Ryan, R.M.; Gargurevich, R.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Jai-Ai, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Wajanatinapart, P.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kacmár, P.; Macapagal, P.M.; Maniaci, M.R.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Parashar, N.; Papachristopoulos, K.; Chartier, C.R.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Mallik, P.R.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Hernandez, A.; Thogersen-Ntoumani, C.; Ntoumanis, N.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Neubauer, A.B.; Martin, N.I.; Torunsky, N.; Van Antwerpen, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Forscher, P.S.; Corral-Frías, N.S.; Ouherrou, N.; Abbas, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kurfali, M.; Kabir, M.; Muda, R.; Del Carmen M. C. Tejada Rivera, M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Arvanitis, A.; Rentzelas, P.; Vansteenkiste, M.; Metz, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Gugliandolo, M.C.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Dunn, M.R.; Korbmacher, M.; Adamkovic, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martoncik, M.; Voracek, M.; Cadek, M.; Frias-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Thomas, A.G.; Kohlová, M.B.; Paruzel-Czachura, M.; Sabristov, M.; Greenburgh, A.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Magrin, M.E.; Jones, M.V.; Li, M.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Stoyanova, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Van Hooff, M.L.M.; Varella, M.A.C.; Standage, M.; Nicolotti, M.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Lu, J.G.; Pineda, L.M.S.; Matos, L.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Smit, E.S.; Kushnir, E.; Wichman, A.L.; Ferguson, L.J.; Anton-Boicuk, L.; De Holanda Coelho, G.L.; Ahlgren, L.; Liga, F.; Levitan, C.A.; Micheli, L.; Gunton, L.-A.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Beatrix, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wylie, K.; Wachowicz, J.; Charyate, A.C.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Belaus, A.; Emmanuel Agesin, B.B.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Morris, K.; Klevjer, K.; Van Schie, K.; Vezirian, K.; Damnjanovic, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Staniaszek, K.; Adetula, A.; Grzech, K.; Hoyer, K.; Moon, K.; Khaobunmasiri, S.; Rana, K.; Janjic, K.; Suchow, J.W.; Kielinska, J.; Cruz Vásquez, J.E.; Chanal, J.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Askelund, A.D.; Pavlacic, J.M.; Benka, J.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Waterschoot, J.; Moss, J.D.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Joy-Gaba, J.A.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Djordjevic, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Groyecka-Bernard, A.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Martela, F.; Foroni, F.; Forest, J.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinova, E.; Strukelj, E.; Etebari, Z.; Bradshaw, E.L.; Baskin, E.; Garcia, E.O.L.; Musser, E.; Van Steenkiste, I.M.M.; Ahn, E.R.; Quested, E.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Sakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popovic, D.; Dunleavy, D.; Djamai, I.; Krupic, D.; Herrera, D.; Vega, D.; Du, H.; Mola, D.; Chakarova, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Boller, D.; Rosa, A.D.; Dimova, D.; Krupic, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; Von Bastian, C.C.; Sutherland, C.A.M.; Ebersole, C.R.; Overkott, C.; Aberson, C.L.; Wang, C.; Niemiec, C.P.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Brownlow, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Ferreyra, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Vermote, B.J.; Bokkour, A.; Bogatyreva, N.; Shi, J.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Bayyat, M.M.; Cocco, B.; Ahmed, A.; Chou, W.-L.; Barkoukis, V.; Hubena, B.; Khaoudi, A.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babincák, P.; Soenens, B.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Ait El Arabi, K.; Özdogru, A.A.; Rothbaum, A.O.; Torres, A.O.; Theodoropoulou, A.; Skowronek, A.; Urooj, A.; Jurkovic, A.P.; Singh, A.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Landry, A.T.; Ferreira, A.; Santos, A.C.; De La Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Luxon, A.M.; Todsen, A.L.; Karababa, A.; Janak, A.; Pilato, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.</t>
-        </is>
-      </c>
+          <t>Single-trial Based EEG Classification of the Dynamic Representation of Speaker Stance: A Preliminary Study with Representational Similarity Analysis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+          <t>NeuroManagement and Intelligent Computing Method on Multimodal Interaction on - ICMI '19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>journal-article</t>
+          <t>conference-paper</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10.1073/pnas.2213828119</t>
+          <t>10.1145/3357160.3357672</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1073/pnas.2213828119</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1145/3357160.3357672</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>From Infant Attachment to God Belief: Rethinking Factors of Trust Underlying the Psychological Origin and Developmental Processes of Religious Belief</t>
+          <t>Open Science as a Better Gatekeeper for Science and Society: A Perspective from Neurolaw</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jiang, X.</t>
+          <t>Hu Chuan-Peng; Xiaoming Jiang; Ricky Jeffrey; Xi-Nian Zuo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Logos and Pneuma - Chinese Journal of Theology</t>
+          <t>Science Bulletin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
+          <t>preprint</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10.31234/osf.io/8dr23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.31234/osf.io/8dr23</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Impacts of aging on suprasegmental and segmental encoding of vocally-expressed confidence in Wuxi dialect</t>
+          <t>The sound of im/politeness</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ji, Y.; Sun, Q.; Peng, Z.; Jiang, X.</t>
+          <t>Jonathan A. Caballero; Nikos Vergis; Xiaoming Jiang; Marc D. Pell</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2022 13th International Symposium on Chinese Spoken Language Processing, ISCSLP 2022</t>
+          <t>Speech Communication</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>conference-paper</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10.1109/ISCSLP57327.2022.10037951</t>
+          <t>10.1016/j.specom.2018.06.004</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ISCSLP57327.2022.10037951</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.specom.2018.06.004</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>In COVID-19 Health Messaging, Loss Framing Increases Anxiety with Little-to-No Concomitant Benefits: Experimental Evidence from 84 Countries</t>
+          <t>Neural architecture underlying person perception from in-group and out-group voices</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dorison, C.A.; Lerner, J.S.; Heller, B.H.; Rothman, A.J.; Kawachi, I.I.; Wang, K.; Rees, V.W.; Gill, B.P.; Gibbs, N.; Ebersole, C.R.; Vally, Z.; Tajchman, Z.; Zsido, A.N.; Zrimsek, M.; Chen, Z.; Ziano, I.; Gialitaki, Z.; Ceary, C.D.; Lin, Y.; Kunisato, Y.; Yamada, Y.; Xiao, Q.; Jiang, X.; Du, X.; Yao, E.; Wilson, J.P.; Cyrus-Lai, W.; Jimenez-Leal, W.; Law, W.; Collins, W.M.; Richard, K.L.; Vranka, M.; Ankushev, V.; Schei, V.; Križanić, V.; Kadreva, V.H.; Adoric, V.C.; Tran, U.S.; Yeung, S.K.; Hassan, W.; Houston, R.; Lima, T.J.S.; Ostermann, T.; Frizzo, T.; Sverdrup, T.E.; House, T.; Gill, T.; Fedotov, M.; Paltrow, T.; Jernsäther, T.; Koptjevskaja-Tamm, M.; Hostler, T.J.; Ishii, T.; Szaszi, B.; Adamus, S.; Suter, L.; Habib, S.; Studzinska, A.; Stojanovska, D.; Janssen, S.M.J.; Stieger, S.; Schulenberg, S.E.; Tatachari, S.; Azouaghe, S.; Sorokowski, P.; Sorokowska, A.; Song, X.; Lewis, S.C.; Sinkolova, S.; Grigoryev, D.; Drexler, S.M.; Daches, S.; Geniole, S.N.; Vračar, S.; Massoni, S.; Zorjan, S.; Sarıoğuz, E.; Izquierdo, S.M.; Alves, S.G.; Pöntinen, S.; Solas, S.Á.; Ordoñez-Riaño, S.; Očovaj, S.B.; Onie, S.; Lins, S.; Çoksan, S.; Sacakli, A.; Ruiz-Fernández, S.; Geiger, S.J.; FatahModares, S.; Walczak, R.B.; Betlehem, R.; Vilar, R.; Cárcamo, R.; Ross, R.M.; McCarthy, R.; Ballantyne, T.; Westgate, E.C.; Afhami, R.; Ren, D.; Monteiro, R.P.; Reips, U.-D.; Reggev, N.; Calin-Jageman, R.J.; Pourafshari, R.; Oliveira, R.; Nedelcheva-Datsova, M.; Rahal, R.-M.; Ribeiro, R.R.; Radtke, T.; Searston, R.; Habte, R.; Zdybek, P.; Chen, S.-C.; Maturan, P.L.G.; Perillo, J.T.; Isager, P.M.; Kačmár, P.; Macapagal, P.M.; Szwed, P.; Hanel, P.H.P.; Forbes, P.A.G.; Arriaga, P.; Paris, B.; Papachristopoulos, K.; Correa, P.S.; Kácha, O.; Bernardo, M.; Campos, O.; Bravo, O.N.; Galindo-Caballero, O.J.; Ogbonnaya, C.E.; Bialobrzeska, O.; Kiselnikova, N.; Simonovic, N.; Cohen, N.; Nock, N.L.; Johannes, N.; Albayrak-Aydemir, N.; Say, N.; Torunsky, N.; Van Doren, N.; Sunami, N.; Rachev, N.R.; Majeed, N.M.; Schmidt, N.-D.; Nadif, K.; Corral-Frías, N.S.; Ouherrou, N.; Pantazi, M.; Lucas, M.Y.; Vasilev, M.R.; Ortiz, M.V.; Butt, M.M.; Kabir, M.; Muda, R.; Tejada Rivera, M.C.M.; Sirota, M.; Seehuus, M.; Parzuchowski, M.; Toro, M.; Hricova, M.; Maldonado, M.A.; Marszalek, M.; Karekla, M.; Mioni, G.; Bosma, M.J.; Westerlund, M.; Vdovic, M.; Bialek, M.; Silan, M.A.; Anne, M.; Misiak, M.; Grinberg, M.; Capizzi, M.; Espinoza Barría, M.F.; Kurfali, M.A.; Mensink, M.C.; Harutyunyan, M.; Khosla, M.; Korbmacher, M.; Adamkovič, M.; Ribeiro, M.F.F.; Terskova, M.; Hruška, M.; Martončik, M.; Voracek, M.; Čadek, M.; Frías-Armenta, M.; Kowal, M.; Topor, M.; Roczniewska, M.; Oosterlinck, M.; Kohlová, M.B.; Paruzel-Czachura, M.; Romanova, M.; Papadatou-Pastou, M.; Lund, M.L.; Antoniadi, M.; Jones, M.V.; Ortiz, M.S.; Manavalan, M.; Muminov, A.; Kossowska, M.; Friedemann, M.; Wielgus, M.; Varella, M.A.C.; Colloff, M.F.; Bradford, M.; Vaughn, L.A.; Eudave, L.; Vieira, L.; Pineda, L.M.S.; Pérez, L.C.; Lazarevic, L.B.; Jaremka, L.M.; Kushnir, E.; Anton-Boicuk, L.; de Holanda Coelho, G.L.; Ahlgren, L.; Levitan, C.A.; Micheli, L.; Volz, L.; Stojanovska, M.; Boucher, L.; Samojlenko, L.; Delgado, L.G.J.; Kaliska, L.; Warmelink, L.; Rojas-Berscia, L.M.; Yu, K.; Wachowicz, J.; Desai, K.; Barzykowski, K.; Kozma, L.; Evans, K.; Kirgizova, K.; Agesin, B.E.; Koehn, M.A.; Wolfe, K.; Korobova, T.; Klevjer, K.; van Schie, K.; Vezirian, K.; Damnjanović, K.; Thommesen, K.K.; Schmidt, K.; Filip, K.; Grzech, K.; Hoyer, K.; Moon, K.; Rana, K.; Janjić, K.; Suchow, J.W.; Kielińska, J.; Cruz Vásquez, J.E.; Beitner, J.; Vargas-Nieto, J.C.; Roxas, J.C.T.; Taber, J.; Urriago-Rayo, J.; Pavlacic, J.M.; Bavolar, J.; Soto, J.A.; Olofsson, J.K.; Vilsmeier, J.K.; Messerschmidt, J.; Czamanski-Cohen, J.; Boudesseul, J.; Lee, J.M.; Kamburidis, J.; Zickfeld, J.; Miranda, J.F.; Verharen, J.P.H.; Hristova, E.; Beshears, J.E.; Đorđević, J.M.; Bosch, J.; Valentova, J.V.; Antfolk, J.; Berkessel, J.B.; Schrötter, J.; Urban, J.; Röer, J.P.; Norton, J.O.; Silva, J.R.; Pickering, J.S.; Vintr, J.; Uttley, J.; Kunst, J.R.; Ndukaihe, I.L.G.; Iyer, A.; Vilares, I.; Ivanov, A.; Ropovik, I.; Sula, I.; Sarieva, I.; Metin-Orta, I.; Prusova, I.; Pinto, I.; Bozdoc, A.I.; Almeida, I.A.T.; Pit, I.L.; Dalgar, I.; Zakharov, I.; Arinze, A.I.; Ihaya, K.; Stephen, I.D.; Gjoneska, B.; Brohmer, H.; Flowe, H.; Godbersen, H.; Kocalar, H.E.; Hedgebeth, M.V.; Chuan-Peng, H.; Sharifian, M.H.; Manley, H.; Akkas, H.; Hajdu, N.; Azab, H.; Kaminski, G.; Nilsonne, G.; Anjum, G.; Travaglino, G.A.; Feldman, G.; Pfuhl, G.; Czarnek, G.; Marcu, G.M.; Hofer, G.; Banik, G.; Adetula, G.A.; Bijlstra, G.; Verbruggen, F.; Kung, F.Y.H.; Foroni, F.; Singer, G.; Muchembled, F.; Azevedo, F.; Mosannenzadeh, F.; Marinov, E.; Štrukelj, E.; Etebari, Z.; Baskin, E.; Garcia, E.O.L.; Musser, E.; van Steenkiste, I.M.M.; Ahn, E.R.; Pronizius, E.; Jackson, E.A.; Manunta, E.; Agadullina, E.; Šakan, D.; Dursun, P.; Dujols, O.; Dubrov, D.; Willis, M.; Tümer, M.; Beaudry, J.L.; Popović, D.; Dunleavy, D.; Djamai, I.; Krupić, D.; Vega, D.; Du, H.; Mola, D.; Davis, W.E.; Holford, D.L.; Lewis, D.M.G.; Vaidis, D.C.; Ozery, D.H.; Ricaurte, D.Z.; Storage, D.; Sousa, D.; Alvarez, D.S.; Rosa, A.D.; Krupić, D.; Marko, D.; Moreau, D.; Reeck, C.; Correia, R.C.; Whitt, C.M.; Lamm, C.; Solorzano, C.S.; von Bastian, C.C.; Sutherland, C.A.; Overkott, C.; Aberson, C.L.; Wang, C.; Karashiali, C.; Noone, C.; Chiu, F.; Picciocchi, C.; Karaarslan, C.; Cellini, N.; Esteban-Serna, C.; Reyna, C.; Batres, C.; Li, R.; Grano, C.; Carpentier, J.; Tamnes, C.K.; Fu, C.H.Y.; Ishkhanyan, B.; Bylinina, L.; Jaeger, B.; Bundt, C.; Allred, T.B.; Bokkour, A.; Bogatyreva, N.; Chopik, W.J.; Antazo, B.; Behzadnia, B.; Becker, M.; Cocco, B.; Chou, W.-L.; Hubena, B.; Žuro, B.; Aczel, B.; Baklanova, E.; Bai, H.; Balci, B.B.; Babinčák, P.; Dixson, B.J.W.; Mokady, A.; Kappes, H.B.; Atari, M.; Szala, A.; Szabelska, A.; Aruta, J.J.B.; Domurat, A.; Arinze, N.C.; Modena, A.; Adiguzel, A.; Monajem, A.; Arabi, K.A.E.; Özdoğru, A.A.; Olaya Torres, A.J.; Theodoropoulou, A.; Jurković, A.P.; Kassianos, A.P.; Findor, A.; Hartanto, A.; Thibault Landry, A.; Ferreira, A.; Santos, A.C.; De la Rosa-Gomez, A.; Gourdon-Kanhukamwe, A.; Todsen, A.L.; Karababa, A.; Janak, A.; Bran, A.; Tullett, A.M.; Kuzminska, A.O.; Krafnick, A.J.; Urooj, A.; Khaoudi, A.; Ahmed, A.; Groyecka-Bernard, A.; Askelund, A.D.; Adetula, A.; Belaus, A.; Charyate, A.C.; Wichman, A.L.; Stoyanova, A.; Greenburgh, A.; Thomas, A.G.; Arvanitis, A.; Forscher, P.S.; Mallik, P.R.; Primbs, M.A.; Miller, J.K.; Moshontz, H.; Urry, H.L.; IJzerman, H.; Basnight-Brown, D.M.; Chartier, C.R.; Buchanan, E.M.; Coles, N.A.</t>
+          <t>Jiang, X.; Sanford, R.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Affective Science</t>
+          <t>NeuroImage</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3328,91 +3714,103 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10.1007/s42761-022-00128-3</t>
+          <t>10.1016/j.neuroimage.2018.07.042</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s42761-022-00128-3</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuroimage.2018.07.042</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Increased spontaneous fronto-central oscillatory power during eye closing in patients with multiple somatic symptoms</t>
+          <t>Predicting confidence and doubt in accented speakers: Human perception and machine learning experiments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ma, X.; Jiang, X.; Jiang, Y.</t>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Psychiatry Research - Neuroimaging</t>
+          <t>Proceedings of the International Conference on Speech Prosody</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>journal-article</t>
+          <t>conference-paper</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10.1016/j.pscychresns.2022.111489</t>
+          <t>10.21437/SpeechProsody.2018-55</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pscychresns.2022.111489</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.21437/SpeechProsody.2018-55</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Neural segregation in left inferior frontal gyrus of semantic processes at different levels of syntactic hierarchy</t>
+          <t>Neural systems for evaluating speaker (Un)believability</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Li, X.; Jiang, X.; Chang, W.; Tan, Y.; Zhou, X.</t>
+          <t>Xiaoming Jiang; Ryan Sanford; Marc D. Pell</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Neuropsychologia</t>
+          <t>Human Brain Mapping</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3422,44 +3820,50 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10.1016/j.neuropsychologia.2022.108254</t>
+          <t>10.1002/hbm.23630</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2022.108254</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1002/hbm.23630</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Resting-state occipito-frontal alpha connectome is linked to differential word learning ability in adult learners</t>
+          <t>A microneedle electrode array on flexible substrate for long-term EEG monitoring</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Huang, Y.; Deng, Y.; Jiang, X.; Chen, Y.; Mao, T.; Xu, Y.; Jiang, C.; Rao, H.</t>
+          <t>Wang, R.; Jiang, X.; Wang, W.; Li, Z.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Frontiers in Neuroscience</t>
+          <t>Sensors and Actuators, B: Chemical</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3469,44 +3873,50 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10.3389/fnins.2022.953315</t>
+          <t>10.1016/j.snb.2017.01.052</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fnins.2022.953315</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.snb.2017.01.052</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Immediate online use of prosody reveals the ironic intentions of a speaker: neurophysiological evidence</t>
+          <t>Effects of contextual relevance on pragmatic inference during conversation: An fMRI study</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mauchand, M.; Caballero, J.A.; Jiang, X.; Pell, M.D.</t>
+          <t>Feng, W.; Wu, Y.; Jan, C.; Yu, H.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cognitive, Affective and Behavioral Neuroscience</t>
+          <t>Brain and Language</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3516,39 +3926,50 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.3758/s13415-020-00849-7</t>
+          <t>10.1016/j.bandl.2017.04.005</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3758/s13415-020-00849-7</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.bandl.2017.04.005</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>An alternative structure rescues failed semantics? Strong global expectancy reduces local-mismatch N400 in Chinese flexible structures</t>
+          <t>Neural correlates of fine-grained meaning distinctions: An fMRI investigation of scalar quantifiers</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Zhan, J.; Jiang, X.; Politzer-Ahles, S.; Zhou, X.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Neuropsychologia</t>
+          <t>Human Brain Mapping</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3558,44 +3979,50 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.1016/j.neuropsychologia.2020.107380</t>
+          <t>10.1002/hbm.23633</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2020.107380</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1002/hbm.23633</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gender interference in processing Chinese compound reflexive: evidence from reading eye-tracking</t>
+          <t>The sound of confidence and doubt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chang, W.; Duan, Y.; Qian, J.; Wu, F.; Jiang, X.; Zhou, X.</t>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Language, Cognition and Neuroscience</t>
+          <t>Speech Communication</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3605,44 +4032,50 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10.1080/23273798.2020.1781213</t>
+          <t>10.1016/j.specom.2017.01.011</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/23273798.2020.1781213</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.specom.2017.01.011</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Neural responses to interpersonal requests: Effects of imposition and vocally-expressed stance</t>
+          <t>Neural responses towards a speaker's feeling of (un)knowing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vergis, N.; Jiang, X.; Pell, M.D.</t>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Brain Research</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3652,44 +4085,50 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.1016/j.brainres.2020.146855</t>
+          <t>10.1016/j.neuropsychologia.2015.12.008</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.brainres.2020.146855</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2015.12.008</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Neurophysiological correlates of sexually evocative speech</t>
+          <t>The feeling of another's knowing: How "Mixed Messages" in speech are reconciled</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rigoulot, S.; Jiang, X.; Vergis, N.; Pell, M.D.</t>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Biological Psychology</t>
+          <t>Journal of Experimental Psychology: Human Perception and Performance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3699,39 +4138,50 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.1016/j.biopsycho.2020.107909</t>
+          <t>10.1037/xhp0000240</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.biopsycho.2020.107909</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1037/xhp0000240</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eye Movements Reveal Delayed Use of Construction-Based Pragmatic Information During Online Sentence Reading: A Case of Chinese Lian…dou Construction</t>
+          <t>More than accuracy: Nonverbal dialects modulate the time course of vocal emotion recognition across cultures</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jiang, X.; Paulmann, S.; Robin, J.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Frontiers in Psychology</t>
+          <t>Journal of Experimental Psychology: Human Perception and Performance</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3741,39 +4191,50 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10.3389/fpsyg.2019.02211</t>
+          <t>10.1037/xhp0000043</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpsyg.2019.02211</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1037/xhp0000043</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Commentary: A Neural Mechanism of Social Categorization</t>
+          <t>On how the brain decodes vocal cues about speaker confidence</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Frontiers in Neuroscience</t>
+          <t>Cortex</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3783,133 +4244,156 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10.3389/fnins.2019.00368</t>
+          <t>10.1016/j.cortex.2015.02.002</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fnins.2019.00368</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.cortex.2015.02.002</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Single-trial Based EEG Classification of the Dynamic Representation of Speaker Stance: A Preliminary Study with Representational Similarity Analysis</t>
+          <t>When a causal assumption is not satisfied by reality: Differential brain responses to concessive and causal relations during sentence comprehension</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Xu, X.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NeuroManagement and Intelligent Computing Method on Multimodal Interaction on - ICMI '19</t>
+          <t>Language, Cognition and Neuroscience</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>conference-paper</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10.1145/3357160.3357672</t>
+          <t>10.1080/23273798.2015.1005636</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3357160.3357672</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1080/23273798.2015.1005636</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Open Science as a Better Gatekeeper for Science and Society: A Perspective from Neurolaw</t>
+          <t>An emotion regulation role of ventromedial prefrontal cortex in moral judgment</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hu Chuan-Peng; Xiaoming Jiang; Ricky Jeffrey; Xi-Nian Zuo</t>
+          <t>Hu, C.; Jiang, X.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Science Bulletin</t>
+          <t>Frontiers in Human Neuroscience</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>preprint</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10.31234/osf.io/8dr23</t>
+          <t>10.3389/fnhum.2014.00873</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://doi.org/10.31234/osf.io/8dr23</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.3389/fnhum.2014.00873</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The sound of im/politeness</t>
+          <t>Cognitive empathy modulates the processing of pragmatic constraints during sentence comprehension</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jonathan A. Caballero; Nikos Vergis; Xiaoming Jiang; Marc D. Pell</t>
+          <t>Li, S.; Jiang, X.; Yu, H.; Zhou, X.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Speech Communication</t>
+          <t>Social Cognitive and Affective Neuroscience</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3919,138 +4403,148 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10.1016/j.specom.2018.06.004</t>
+          <t>10.1093/scan/nst091</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.specom.2018.06.004</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1093/scan/nst091</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Neural architecture underlying person perception from in-group and out-group voices</t>
+          <t>Encoding and decoding confidence information in speech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jiang, X.; Sanford, R.; Pell, M.D.</t>
+          <t>Jiang, X.; Pell, M.D.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NeuroImage</t>
+          <t>Proceedings of the International Conference on Speech Prosody</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuroimage.2018.07.042</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuroimage.2018.07.042</t>
-        </is>
-      </c>
+          <t>conference-paper</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Predicting confidence and doubt in accented speakers: Human perception and machine learning experiments</t>
+          <t>Distinct neural correlates for pragmatic and semantic meaning processing: An event-related potential investigation of scalar implicature processing using picture-sentence verification</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jiang, X.; Pell, M.D.</t>
+          <t>Politzer-Ahles, S.; Fiorentino, R.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Proceedings of the International Conference on Speech Prosody</t>
+          <t>Brain Research</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>conference-paper</t>
+          <t>journal-article</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10.21437/SpeechProsody.2018-55</t>
+          <t>10.1016/j.brainres.2012.10.042</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21437/SpeechProsody.2018-55</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.brainres.2012.10.042</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Neural systems for evaluating speaker (Un)believability</t>
+          <t>Even a rich man can afford that expensive house: ERP responses to construction-based pragmatic constraints during sentence comprehension</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Xiaoming Jiang; Ryan Sanford; Marc D. Pell</t>
+          <t>Jiang, X.; Li, Y.; Zhou, X.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Human Brain Mapping</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4060,44 +4554,50 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10.1002/hbm.23630</t>
+          <t>10.1016/j.neuropsychologia.2013.06.009</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hbm.23630</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2013.06.009</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A microneedle electrode array on flexible substrate for long-term EEG monitoring</t>
+          <t>Is it over-respectful or disrespectful? Differential patterns of brain activity in perceiving pragmatic violation of social status information during utterance comprehension</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wang, R.; Jiang, X.; Wang, W.; Li, Z.</t>
+          <t>Jiang, X.; Li, Y.; Zhou, X.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sensors and Actuators, B: Chemical</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4107,44 +4607,50 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10.1016/j.snb.2017.01.052</t>
+          <t>10.1016/j.neuropsychologia.2013.07.021</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.snb.2017.01.052</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2013.07.021</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Effects of contextual relevance on pragmatic inference during conversation: An fMRI study</t>
+          <t>Processing biological gender and number information during Chinese pronoun resolution: ERP evidence for functional differentiation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Feng, W.; Wu, Y.; Jan, C.; Yu, H.; Jiang, X.; Zhou, X.</t>
+          <t>Xu, X.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Brain and Language</t>
+          <t>Brain and Cognition</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4154,44 +4660,50 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10.1016/j.bandl.2017.04.005</t>
+          <t>10.1016/j.bandc.2012.11.002</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.bandl.2017.04.005</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.bandc.2012.11.002</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Neural correlates of fine-grained meaning distinctions: An fMRI investigation of scalar quantifiers</t>
+          <t>Multiple semantic processes at different levels of syntactic hierarchy: Does the higher-level process proceed in face of a lower-level failure?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Zhan, J.; Jiang, X.; Politzer-Ahles, S.; Zhou, X.</t>
+          <t>Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Human Brain Mapping</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4201,44 +4713,50 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10.1002/hbm.23633</t>
+          <t>10.1016/j.neuropsychologia.2012.04.016</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/hbm.23633</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2012.04.016</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The sound of confidence and doubt</t>
+          <t>To believe or not to believe: Trust choice modulates brain responses in outcome evaluation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jiang, X.; Pell, M.D.</t>
+          <t>Long, Y.; Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Speech Communication</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4248,44 +4766,50 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10.1016/j.specom.2017.01.011</t>
+          <t>10.1016/j.neuroscience.2011.10.035</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.specom.2017.01.011</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuroscience.2011.10.035</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Neural responses towards a speaker's feeling of (un)knowing</t>
+          <t>Multiple constraints on semantic integration in a hierarchical structure: ERP evidence from German</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jiang, X.; Pell, M.D.</t>
+          <t>Zhang, Y.; Jiang, X.; Saalbach, H.; Zhou, X.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Neuropsychologia</t>
+          <t>Brain Research</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4295,44 +4819,50 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10.1016/j.neuropsychologia.2015.12.008</t>
+          <t>10.1016/j.brainres.2011.06.061</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2015.12.008</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.brainres.2011.06.061</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The feeling of another's knowing: How "Mixed Messages" in speech are reconciled</t>
+          <t>Semantic integration processes at different levels of syntactic hierarchy during sentence comprehension: An ERP study</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jiang, X.; Pell, M.D.</t>
+          <t>Zhou, X.; Jiang, X.; Ye, Z.; Zhang, Y.; Lou, K.; Zhan, W.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Journal of Experimental Psychology: Human Perception and Performance</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4342,44 +4872,50 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10.1037/xhp0000240</t>
+          <t>10.1016/j.neuropsychologia.2010.02.001</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1037/xhp0000240</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2010.02.001</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>More than accuracy: Nonverbal dialects modulate the time course of vocal emotion recognition across cultures</t>
+          <t>Processing different levels of syntactic hierarchy: An ERP study on Chinese</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jiang, X.; Paulmann, S.; Robin, J.; Pell, M.D.</t>
+          <t>Jiang, X.; Zhou, X.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Journal of Experimental Psychology: Human Perception and Performance</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4389,44 +4925,50 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10.1037/xhp0000043</t>
+          <t>10.1016/j.neuropsychologia.2009.01.013</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1037/xhp0000043</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2009.01.013</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>On how the brain decodes vocal cues about speaker confidence</t>
+          <t>Processing the universal quantifier during sentence comprehension: ERP evidence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jiang, X.; Pell, M.D.</t>
+          <t>Jiang, X.; Tan, Y.; Zhou, X.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cortex</t>
+          <t>Neuropsychologia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4436,672 +4978,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>10.1016/j.cortex.2015.02.002</t>
+          <t>10.1016/j.neuropsychologia.2009.02.020</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.cortex.2015.02.002</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1016/j.neuropsychologia.2009.02.020</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>When a causal assumption is not satisfied by reality: Differential brain responses to concessive and causal relations during sentence comprehension</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Xu, X.; Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Language, Cognition and Neuroscience</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>10.1080/23273798.2015.1005636</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/23273798.2015.1005636</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>An emotion regulation role of ventromedial prefrontal cortex in moral judgment</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Hu, C.; Jiang, X.</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Frontiers in Human Neuroscience</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>10.3389/fnhum.2014.00873</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3389/fnhum.2014.00873</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Cognitive empathy modulates the processing of pragmatic constraints during sentence comprehension</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Li, S.; Jiang, X.; Yu, H.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Social Cognitive and Affective Neuroscience</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>10.1093/scan/nst091</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/scan/nst091</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Encoding and decoding confidence information in speech</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Pell, M.D.</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Proceedings of the International Conference on Speech Prosody</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>conference-paper</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Distinct neural correlates for pragmatic and semantic meaning processing: An event-related potential investigation of scalar implicature processing using picture-sentence verification</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Politzer-Ahles, S.; Fiorentino, R.; Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Brain Research</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10.1016/j.brainres.2012.10.042</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.brainres.2012.10.042</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Even a rich man can afford that expensive house: ERP responses to construction-based pragmatic constraints during sentence comprehension</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Li, Y.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2013.06.009</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2013.06.009</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Is it over-respectful or disrespectful? Differential patterns of brain activity in perceiving pragmatic violation of social status information during utterance comprehension</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Li, Y.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2013.07.021</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2013.07.021</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Processing biological gender and number information during Chinese pronoun resolution: ERP evidence for functional differentiation</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Xu, X.; Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Brain and Cognition</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>10.1016/j.bandc.2012.11.002</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.bandc.2012.11.002</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Multiple semantic processes at different levels of syntactic hierarchy: Does the higher-level process proceed in face of a lower-level failure?</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2012.04.016</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2012.04.016</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>To believe or not to believe: Trust choice modulates brain responses in outcome evaluation</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Long, Y.; Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Neuroscience</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuroscience.2011.10.035</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuroscience.2011.10.035</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Multiple constraints on semantic integration in a hierarchical structure: ERP evidence from German</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Zhang, Y.; Jiang, X.; Saalbach, H.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Brain Research</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>10.1016/j.brainres.2011.06.061</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.brainres.2011.06.061</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Semantic integration processes at different levels of syntactic hierarchy during sentence comprehension: An ERP study</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Zhou, X.; Jiang, X.; Ye, Z.; Zhang, Y.; Lou, K.; Zhan, W.</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2010.02.001</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2010.02.001</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Processing different levels of syntactic hierarchy: An ERP study on Chinese</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2009.01.013</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2009.01.013</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Processing the universal quantifier during sentence comprehension: ERP evidence</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Jiang, X.; Tan, Y.; Zhou, X.</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Neuropsychologia</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>journal-article</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>10.1016/j.neuropsychologia.2009.02.020</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.neuropsychologia.2009.02.020</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>0000-0002-5171-9774</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5898,7 +5798,6 @@
           <t>https://www.mcgill.ca/scsd/marc-d-pell-phd</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5929,7 +5828,6 @@
           <t>https://lt.cityu.edu.hk/people/academic-staff/li-jixing</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5960,7 +5858,6 @@
           <t>https://www.angl.hu-berlin.de/department/staff-faculty/professors/liu</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5986,7 +5883,6 @@
           <t>PhD candidate, ETH Zürich</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6012,7 +5908,6 @@
           <t>PhD candidate, University of Cambridge</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6043,7 +5938,6 @@
           <t>https://wenjunchen29.github.io/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>yes</t>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -688,22 +688,16 @@
           <t>https://doi.org/10.1016/j.lingua.2026.104185</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -721,7 +715,6 @@
           <t>Tianze Xu; Xiaoming Jiang; Volker Dellwo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -737,22 +730,16 @@
           <t>https://doi.org/10.31234/osf.io/4zrwy_v3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -790,22 +777,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2026.121987</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -843,22 +824,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2026.109493</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -896,22 +871,16 @@
           <t>https://doi.org/10.1044/2025_JSLHR-25-00294</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -929,7 +898,6 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -945,22 +913,16 @@
           <t>https://doi.org/10.64898/2026.04.08.716483</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -998,22 +960,16 @@
           <t>https://doi.org/10.1016/j.bandl.2026.105723</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1051,22 +1007,16 @@
           <t>https://doi.org/10.1016/j.chbah.2026.100261</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1104,22 +1054,16 @@
           <t>https://doi.org/10.1371/journal.pone.0327529</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1157,22 +1101,16 @@
           <t>https://doi.org/10.1038/s41597-025-06110-5</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1210,22 +1148,16 @@
           <t>https://doi.org/10.1044/2025_JSLHR-24-00849</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1263,22 +1195,16 @@
           <t>https://doi.org/10.1186/s40359-025-03522-1</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1296,7 +1222,6 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -1312,22 +1237,16 @@
           <t>https://doi.org/10.20944/preprints202510.1492.v1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1365,22 +1284,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2025.121253</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1418,22 +1331,16 @@
           <t>https://doi.org/10.3390/languages10060119</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1471,22 +1378,16 @@
           <t>https://doi.org/10.3758/s13428-025-02608-3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1524,22 +1425,16 @@
           <t>https://doi.org/10.1121/10.0032400</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1577,22 +1472,16 @@
           <t>https://doi.org/10.1016/j.tics.2024.08.005</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1630,22 +1519,16 @@
           <t>https://doi.org/10.3390/bs14080686</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1683,22 +1566,16 @@
           <t>https://doi.org/10.1057/s41599-024-03502-7</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1736,22 +1613,16 @@
           <t>https://doi.org/10.3390/brainsci14030264</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1789,22 +1660,16 @@
           <t>https://doi.org/10.1044/2024_JSLHR-23-00553</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1842,22 +1707,16 @@
           <t>https://doi.org/10.3791/66913</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1895,22 +1754,16 @@
           <t>https://doi.org/10.1016/j.aip.2024.102167</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1928,7 +1781,6 @@
           <t>Wenjun Chen; Xiaoming Jiang</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -1944,22 +1796,16 @@
           <t>https://doi.org/10.20944/preprints202312.0807.v1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1997,22 +1843,16 @@
           <t>https://doi.org/10.20944/preprints202303.0517.v1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2050,22 +1890,16 @@
           <t>https://doi.org/10.1007/s12144-022-03528-7</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2103,22 +1937,16 @@
           <t>https://doi.org/10.1007/s10919-023-00428-7</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2156,22 +1984,16 @@
           <t>https://doi.org/10.3389/fpsyg.2023.1289045</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2209,22 +2031,16 @@
           <t>https://doi.org/10.1016/j.actpsy.2023.103955</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2262,22 +2078,16 @@
           <t>https://doi.org/10.3390/brainsci13121724</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2315,22 +2125,16 @@
           <t>https://doi.org/10.1038/s41597-022-01811-7</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2368,22 +2172,16 @@
           <t>https://doi.org/10.1016/j.jneuroling.2023.101143</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2421,22 +2219,16 @@
           <t>https://doi.org/10.1016/j.pragma.2023.07.005</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2474,22 +2266,16 @@
           <t>https://doi.org/10.1073/pnas.2111091119</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2527,22 +2313,16 @@
           <t>https://doi.org/10.21437/Interspeech.2022-10531</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2580,22 +2360,16 @@
           <t>https://doi.org/10.1016/j.cortex.2021.12.017</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2633,22 +2407,16 @@
           <t>https://doi.org/10.1073/pnas.2213828119</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2676,24 +2444,16 @@
           <t>journal-article</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2731,22 +2491,16 @@
           <t>https://doi.org/10.1109/ISCSLP57327.2022.10037951</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2784,22 +2538,16 @@
           <t>https://doi.org/10.1007/s42761-022-00128-3</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2837,22 +2585,16 @@
           <t>https://doi.org/10.1016/j.pscychresns.2022.111489</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2890,22 +2632,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2022.108254</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2943,22 +2679,16 @@
           <t>https://doi.org/10.3389/fnins.2022.953315</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2996,22 +2726,16 @@
           <t>https://doi.org/10.3389/fpsyg.2022.1028106</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3049,22 +2773,16 @@
           <t>https://doi.org/10.1080/17470919.2021.1938667</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3102,22 +2820,16 @@
           <t>https://doi.org/10.3758/s13415-020-00849-7</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3155,22 +2867,16 @@
           <t>https://doi.org/10.1177/0022022121990897</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3183,7 +2889,6 @@
           <t>An alternative structure rescues failed semantics? Strong global expectancy reduces local-mismatch N400 in Chinese flexible structures</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Neuropsychologia</t>
@@ -3204,22 +2909,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2020.107380</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3257,22 +2956,16 @@
           <t>https://doi.org/10.1080/23273798.2020.1781213</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3310,22 +3003,16 @@
           <t>https://doi.org/10.1016/j.brainres.2020.146855</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3363,22 +3050,16 @@
           <t>https://doi.org/10.1016/j.biopsycho.2020.107909</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3416,22 +3097,16 @@
           <t>https://doi.org/10.1177/1747021819865833</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3444,7 +3119,6 @@
           <t>Eye Movements Reveal Delayed Use of Construction-Based Pragmatic Information During Online Sentence Reading: A Case of Chinese Lian…dou Construction</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Frontiers in Psychology</t>
@@ -3465,22 +3139,16 @@
           <t>https://doi.org/10.3389/fpsyg.2019.02211</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3493,7 +3161,6 @@
           <t>Commentary: A Neural Mechanism of Social Categorization</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Frontiers in Neuroscience</t>
@@ -3514,22 +3181,16 @@
           <t>https://doi.org/10.3389/fnins.2019.00368</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3542,7 +3203,6 @@
           <t>Single-trial Based EEG Classification of the Dynamic Representation of Speaker Stance: A Preliminary Study with Representational Similarity Analysis</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>NeuroManagement and Intelligent Computing Method on Multimodal Interaction on - ICMI '19</t>
@@ -3563,22 +3223,16 @@
           <t>https://doi.org/10.1145/3357160.3357672</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3616,22 +3270,16 @@
           <t>https://doi.org/10.31234/osf.io/8dr23</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3669,22 +3317,16 @@
           <t>https://doi.org/10.1016/j.specom.2018.06.004</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3722,22 +3364,16 @@
           <t>https://doi.org/10.1016/j.neuroimage.2018.07.042</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3775,22 +3411,16 @@
           <t>https://doi.org/10.21437/SpeechProsody.2018-55</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3828,22 +3458,16 @@
           <t>https://doi.org/10.1002/hbm.23630</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3881,22 +3505,16 @@
           <t>https://doi.org/10.1016/j.snb.2017.01.052</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3934,22 +3552,16 @@
           <t>https://doi.org/10.1016/j.bandl.2017.04.005</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3987,22 +3599,16 @@
           <t>https://doi.org/10.1002/hbm.23633</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4040,22 +3646,16 @@
           <t>https://doi.org/10.1016/j.specom.2017.01.011</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4093,22 +3693,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2015.12.008</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4146,22 +3740,16 @@
           <t>https://doi.org/10.1037/xhp0000240</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4199,22 +3787,16 @@
           <t>https://doi.org/10.1037/xhp0000043</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4252,22 +3834,16 @@
           <t>https://doi.org/10.1016/j.cortex.2015.02.002</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4305,22 +3881,16 @@
           <t>https://doi.org/10.1080/23273798.2015.1005636</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4358,22 +3928,16 @@
           <t>https://doi.org/10.3389/fnhum.2014.00873</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4411,22 +3975,16 @@
           <t>https://doi.org/10.1093/scan/nst091</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4454,24 +4012,16 @@
           <t>conference-paper</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4509,22 +4059,16 @@
           <t>https://doi.org/10.1016/j.brainres.2012.10.042</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4562,22 +4106,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.06.009</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4615,22 +4153,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.07.021</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4668,22 +4200,16 @@
           <t>https://doi.org/10.1016/j.bandc.2012.11.002</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4721,22 +4247,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2012.04.016</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4774,22 +4294,16 @@
           <t>https://doi.org/10.1016/j.neuroscience.2011.10.035</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4827,22 +4341,16 @@
           <t>https://doi.org/10.1016/j.brainres.2011.06.061</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4880,22 +4388,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2010.02.001</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4933,22 +4435,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.01.013</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4986,22 +4482,16 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.02.020</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5422,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5468,6 +4958,11 @@
           <t>show</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="31.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -5540,6 +5035,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ph-microphone-stage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5575,6 +5075,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ph-chats-circle</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5610,6 +5115,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ph-cpu</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5645,6 +5155,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ph-globe-hemisphere-east</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5678,6 +5193,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ph-head-circuit</t>
         </is>
       </c>
     </row>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -5652,7 +5652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Chinese tag (e.g. 国际合作招募)</t>
+          <t>加入我们</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>English tag</t>
+          <t>Join us</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>国际合作招募</t>
+          <t>加入我们</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Int'l Recruitment</t>
+          <t>Join us</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>博士招生</t>
+          <t>加入我们</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ph.D. Admissions</t>
+          <t>Join us</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5903,6 +5903,168 @@
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>加入我们</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Join us</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>博士后招聘</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Postdoctoral positions</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>课题组招收博士后研究员，方向涵盖心理语言学、神经语言学与神经语用学。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>We welcome postdoctoral researchers in psycholinguistics, neurolinguistics, and neuropragmatics.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>详细信息后续补充。意向者请邮件联系蒋晓鸣教授 (xiaoming.jiang@shisu.edu.cn)，附 CV 与一份简要研究兴趣陈述。</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Details to be added soon. Interested candidates please email Prof. Xiaoming Jiang (xiaoming.jiang@shisu.edu.cn) with a CV and a brief research statement.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>加入我们</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Join us</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>硕士研究生招生</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Master's admissions</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>课题组通过上海外国语大学语言科学研究院招收硕士研究生，方向以心理与神经语言学为主。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Master's students join the lab through SISU's Institute of Language Sciences MA program, focusing on psycho- and neurolinguistics.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>详细信息后续补充。意向者请邮件联系蒋老师，附本科背景说明、研究兴趣与中英文成绩单。</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Details to be added soon. Please email Prof. Jiang with your undergraduate background, research interests, and Chinese / English transcripts.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>加入我们</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Join us</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>本科生研究助理</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Undergraduate research assistantships</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>课题组定期接收本科生作为研究助理，方向涵盖嗓音情绪、神经语用与跨语言加工。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>We regularly host undergraduate research assistants on projects in vocal emotion, neuropragmatics, and cross-linguistic processing.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>详细信息后续补充。意向者请邮件联系蒋老师，附 GPA、课程背景与可参与的时段。</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Details to be added soon. Please email Prof. Jiang with your GPA, course background, and your availability.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -1848,6 +1848,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
@@ -3273,6 +3278,11 @@
       <c r="K59" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>journal</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5914,7 +5924,6 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>加入我们</t>
@@ -5955,7 +5964,6 @@
           <t>Details to be added soon. Interested candidates please email Prof. Xiaoming Jiang (xiaoming.jiang@shisu.edu.cn) with a CV and a brief research statement.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5968,7 +5976,6 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>加入我们</t>
@@ -6009,7 +6016,6 @@
           <t>Details to be added soon. Please email Prof. Jiang with your undergraduate background, research interests, and Chinese / English transcripts.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6022,7 +6028,6 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>加入我们</t>
@@ -6063,7 +6068,6 @@
           <t>Details to be added soon. Please email Prof. Jiang with your GPA, course background, and your availability.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>yes</t>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -4514,7 +4514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4669,6 +4669,21 @@
           <t>show</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>secondary_title_zh</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>secondary_title_en</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>researchgate</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="31.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -4835,12 +4850,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>上海外国语大学 语言科学研究院｜心理与神经语言学研究中心</t>
+          <t>上海外国语大学</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Institute of Language Sciences, SISU｜Research Center of Psycholinguistics &amp; Neurolinguistics</t>
+          <t>Shanghai International Studies University</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4901,6 +4916,21 @@
       <c r="Z3" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>上海外国语大学语言科学研究院 副院长</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Vice Dean, Institute of Language Sciences, SISU</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Xiaoming-Jiang-3</t>
         </is>
       </c>
     </row>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -4514,7 +4514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4941,6 +4941,243 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tianze-xu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>alumni</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>undergrad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>许天泽</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tianze Xu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://www.cl.uzh.ch/de/about-us/people/team/phonetics/Timothy-Tianze-Xu.html</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>苏黎世大学 博士研究生 / PhD candidate, University of Zurich</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2020–2024</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>苏黎世大学 博士研究生 / PhD candidate, University of Zurich</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>yi-li</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>alumni</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>李怡</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yi Li</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://www.mrc-cbu.cam.ac.uk/people/yi.li/</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>剑桥大学 博士研究生 / PhD candidate, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2021–2024</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>剑桥大学 博士研究生 / PhD candidate, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>wenjun-chen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>alumni</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>陈文均</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wenjun Chen</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://www.mcgill.ca/scsd/wenjun-chen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>麦吉尔大学 博士研究生 / PhD candidate, McGill University</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2021–2024</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>麦吉尔大学 博士研究生 / PhD candidate, McGill University</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5445,7 +5682,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5707,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5737,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -4972,20 +4972,6 @@
           <t>Tianze Xu</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>https://www.cl.uzh.ch/de/about-us/people/team/phonetics/Timothy-Tianze-Xu.html</t>
@@ -5016,9 +5002,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5051,20 +5034,6 @@
           <t>Yi Li</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>https://www.mrc-cbu.cam.ac.uk/people/yi.li/</t>
@@ -5095,9 +5064,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5130,20 +5096,6 @@
           <t>Wenjun Chen</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>https://www.mcgill.ca/scsd/wenjun-chen</t>
@@ -5174,9 +5126,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5752,7 +5701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5794,37 +5743,37 @@
           <t>show</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="27.6" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Funder name (Chinese + English)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>filename in assets/images/logos/ (or blank for text-only)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Hover tooltip with project details if any</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>e.g. 2023-2026 or ongoing</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>External URL (optional)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>国家语言文字工作委员会 / National Language Commission</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国家语言文字工作委员会</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.ywky.edu.cn/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5835,12 +5784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nsfc.png</t>
+          <t>nsfc.jpg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>国家自然科学基金面上项目 (NSFC General Program)</t>
+          <t>National Natural Science Foundation of China</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5853,26 +5802,25 @@
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>国家社科基金 / NSSFC</t>
+          <t>国家社会科学基金 / NSSFC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nssfc.png</t>
+          <t>nssfc.jpg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>国家社科基金重大项目（参与）/ National Social Science Fund of China (Major Project, participated)</t>
+          <t>National Social Science Fund of China</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5882,40 +5830,105 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>http://www.nopss.gov.cn/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+          <t>https://www.nopss.gov.cn/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>上海市曙光计划 / Shanghai Chenguang Program</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>chenguang.jpg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Shanghai Chenguang Scholar Program</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://edu.sh.gov.cn/xxgk2_zdgz_xxkxyj/index.html</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>上海市科学技术委员会 / STCSM</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Shanghai Science and Technology Commission — Shanghai Sci-tech Co-research Program</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>stcsm.png</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Shanghai Science and Technology Committee — Sci-tech Co-research Program</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://stcsm.sh.gov.cn/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>上海市哲学社会科学规划办公室 / Shanghai Planning Office of Philosophy and Social Science</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>shpopss.jpg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Shanghai Planning Office of Philosophy and Social Science</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.sh-popss.gov.cn/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -4514,7 +4514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4684,6 +4684,26 @@
           <t>researchgate</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>mid_zh</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mid_en</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>now_zh</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>now_en</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="31.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -4977,11 +4997,7 @@
           <t>https://www.cl.uzh.ch/de/about-us/people/team/phonetics/Timothy-Tianze-Xu.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>苏黎世大学 博士研究生 / PhD candidate, University of Zurich</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>2020–2024</t>
@@ -4992,14 +5008,30 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>苏黎世大学 博士研究生 / PhD candidate, University of Zurich</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>剑桥大学 MPhil 2024–2025</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>MPhil, University of Cambridge, 2024–2025</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>苏黎世大学 博士研究生（自 2025 起）</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>PhD candidate, University of Zurich (since 2025)</t>
         </is>
       </c>
     </row>
@@ -5039,11 +5071,7 @@
           <t>https://www.mrc-cbu.cam.ac.uk/people/yi.li/</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>剑桥大学 博士研究生 / PhD candidate, University of Cambridge</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>2021–2024</t>
@@ -5054,14 +5082,22 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>剑桥大学 博士研究生 / PhD candidate, University of Cambridge</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>剑桥大学 博士研究生（自 2024 起）</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>PhD candidate, University of Cambridge (since 2024)</t>
         </is>
       </c>
     </row>
@@ -5101,11 +5137,7 @@
           <t>https://www.mcgill.ca/scsd/wenjun-chen</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>麦吉尔大学 博士研究生 / PhD candidate, McGill University</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>2021–2024</t>
@@ -5116,14 +5148,22 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>麦吉尔大学 博士研究生 / PhD candidate, McGill University</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>麦吉尔大学 博士研究生（自 2024 起）</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>PhD candidate, McGill University (since 2024)</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5795,6 @@
           <t>国家语言文字工作委员会 / National Language Commission</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>国家语言文字工作委员会</t>
@@ -5771,7 +5810,6 @@
           <t>https://www.ywky.edu.cn/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>1</v>
       </c>
@@ -5802,7 +5840,6 @@
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>2</v>
       </c>
@@ -5833,7 +5870,6 @@
           <t>https://www.nopss.gov.cn/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>3</v>
       </c>
@@ -5864,7 +5900,6 @@
           <t>https://edu.sh.gov.cn/xxgk2_zdgz_xxkxyj/index.html</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>4</v>
       </c>
@@ -5895,7 +5930,6 @@
           <t>https://stcsm.sh.gov.cn/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>5</v>
       </c>
@@ -5926,7 +5960,6 @@
           <t>https://www.sh-popss.gov.cn/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>6</v>
       </c>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -4868,16 +4868,8 @@
           <t>Professor · Doctoral Supervisor</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>上海外国语大学</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Shanghai International Studies University</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>主要从事心理与神经语言学的科学研究与人才培养工作。研究方向：心理与神经语言学、实验语言学、言语交际与言语障碍、嗓音编码与解码、神经语用学。</t>
@@ -4997,7 +4989,6 @@
           <t>https://www.cl.uzh.ch/de/about-us/people/team/phonetics/Timothy-Tianze-Xu.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>2020–2024</t>
@@ -5008,7 +4999,6 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5071,7 +5061,6 @@
           <t>https://www.mrc-cbu.cam.ac.uk/people/yi.li/</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>2021–2024</t>
@@ -5082,14 +5071,11 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
           <t>剑桥大学 博士研究生（自 2024 起）</t>
@@ -5137,7 +5123,6 @@
           <t>https://www.mcgill.ca/scsd/wenjun-chen</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>2021–2024</t>
@@ -5148,14 +5133,11 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
           <t>麦吉尔大学 博士研究生（自 2024 起）</t>

--- a/site_data.xlsx
+++ b/site_data.xlsx
@@ -688,16 +688,22 @@
           <t>https://doi.org/10.1016/j.lingua.2026.104185</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -715,6 +721,7 @@
           <t>Tianze Xu; Xiaoming Jiang; Volker Dellwo</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -730,16 +737,22 @@
           <t>https://doi.org/10.31234/osf.io/4zrwy_v3</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,16 +790,22 @@
           <t>https://doi.org/10.1016/j.neuroimage.2026.121987</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -824,16 +843,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2026.109493</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -871,16 +896,22 @@
           <t>https://doi.org/10.1044/2025_JSLHR-25-00294</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -898,6 +929,7 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -913,16 +945,22 @@
           <t>https://doi.org/10.64898/2026.04.08.716483</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -960,16 +998,22 @@
           <t>https://doi.org/10.1016/j.bandl.2026.105723</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1007,16 +1051,22 @@
           <t>https://doi.org/10.1016/j.chbah.2026.100261</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1054,16 +1104,22 @@
           <t>https://doi.org/10.1371/journal.pone.0327529</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1101,16 +1157,22 @@
           <t>https://doi.org/10.1038/s41597-025-06110-5</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1148,16 +1210,22 @@
           <t>https://doi.org/10.1044/2025_JSLHR-24-00849</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1195,16 +1263,22 @@
           <t>https://doi.org/10.1186/s40359-025-03522-1</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1222,6 +1296,7 @@
           <t>Wenjun Chen; Marc D. Pell; Xiaoming Jiang</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -1237,16 +1312,22 @@
           <t>https://doi.org/10.20944/preprints202510.1492.v1</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1284,16 +1365,22 @@
           <t>https://doi.org/10.1016/j.neuroimage.2025.121253</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1331,16 +1418,22 @@
           <t>https://doi.org/10.3390/languages10060119</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1378,16 +1471,22 @@
           <t>https://doi.org/10.3758/s13428-025-02608-3</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1425,16 +1524,22 @@
           <t>https://doi.org/10.1121/10.0032400</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,16 +1577,22 @@
           <t>https://doi.org/10.1016/j.tics.2024.08.005</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1519,16 +1630,22 @@
           <t>https://doi.org/10.3390/bs14080686</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1566,16 +1683,22 @@
           <t>https://doi.org/10.1057/s41599-024-03502-7</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1613,16 +1736,22 @@
           <t>https://doi.org/10.3390/brainsci14030264</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1660,16 +1789,22 @@
           <t>https://doi.org/10.1044/2024_JSLHR-23-00553</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1707,16 +1842,22 @@
           <t>https://doi.org/10.3791/66913</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1754,16 +1895,22 @@
           <t>https://doi.org/10.1016/j.aip.2024.102167</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1781,6 +1928,7 @@
           <t>Wenjun Chen; Xiaoming Jiang</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>preprint</t>
@@ -1796,16 +1944,22 @@
           <t>https://doi.org/10.20944/preprints202312.0807.v1</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1843,6 +1997,9 @@
           <t>https://doi.org/10.20944/preprints202303.0517.v1</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1853,11 +2010,13 @@
           <t>journal</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1895,16 +2054,22 @@
           <t>https://doi.org/10.1007/s12144-022-03528-7</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1942,16 +2107,22 @@
           <t>https://doi.org/10.1007/s10919-023-00428-7</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1989,16 +2160,22 @@
           <t>https://doi.org/10.3389/fpsyg.2023.1289045</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2036,16 +2213,22 @@
           <t>https://doi.org/10.1016/j.actpsy.2023.103955</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2083,16 +2266,22 @@
           <t>https://doi.org/10.3390/brainsci13121724</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2130,16 +2319,22 @@
           <t>https://doi.org/10.1038/s41597-022-01811-7</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2177,16 +2372,22 @@
           <t>https://doi.org/10.1016/j.jneuroling.2023.101143</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2224,16 +2425,22 @@
           <t>https://doi.org/10.1016/j.pragma.2023.07.005</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2271,16 +2478,22 @@
           <t>https://doi.org/10.1073/pnas.2111091119</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2318,16 +2531,22 @@
           <t>https://doi.org/10.21437/Interspeech.2022-10531</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2365,16 +2584,22 @@
           <t>https://doi.org/10.1016/j.cortex.2021.12.017</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2412,16 +2637,22 @@
           <t>https://doi.org/10.1073/pnas.2213828119</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2449,16 +2680,24 @@
           <t>journal-article</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2496,16 +2735,22 @@
           <t>https://doi.org/10.1109/ISCSLP57327.2022.10037951</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2543,16 +2788,22 @@
           <t>https://doi.org/10.1007/s42761-022-00128-3</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2590,16 +2841,22 @@
           <t>https://doi.org/10.1016/j.pscychresns.2022.111489</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2637,16 +2894,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2022.108254</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2684,16 +2947,22 @@
           <t>https://doi.org/10.3389/fnins.2022.953315</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2731,16 +3000,22 @@
           <t>https://doi.org/10.3389/fpsyg.2022.1028106</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2778,16 +3053,22 @@
           <t>https://doi.org/10.1080/17470919.2021.1938667</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2825,16 +3106,22 @@
           <t>https://doi.org/10.3758/s13415-020-00849-7</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2872,16 +3159,22 @@
           <t>https://doi.org/10.1177/0022022121990897</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2894,6 +3187,7 @@
           <t>An alternative structure rescues failed semantics? Strong global expectancy reduces local-mismatch N400 in Chinese flexible structures</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Neuropsychologia</t>
@@ -2914,16 +3208,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2020.107380</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2961,16 +3261,22 @@
           <t>https://doi.org/10.1080/23273798.2020.1781213</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3008,16 +3314,22 @@
           <t>https://doi.org/10.1016/j.brainres.2020.146855</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3055,16 +3367,22 @@
           <t>https://doi.org/10.1016/j.biopsycho.2020.107909</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3102,16 +3420,22 @@
           <t>https://doi.org/10.1177/1747021819865833</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3124,6 +3448,7 @@
           <t>Eye Movements Reveal Delayed Use of Construction-Based Pragmatic Information During Online Sentence Reading: A Case of Chinese Lian…dou Construction</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Frontiers in Psychology</t>
@@ -3144,16 +3469,22 @@
           <t>https://doi.org/10.3389/fpsyg.2019.02211</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3166,6 +3497,7 @@
           <t>Commentary: A Neural Mechanism of Social Categorization</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Frontiers in Neuroscience</t>
@@ -3186,16 +3518,22 @@
           <t>https://doi.org/10.3389/fnins.2019.00368</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3208,6 +3546,7 @@
           <t>Single-trial Based EEG Classification of the Dynamic Representation of Speaker Stance: A Preliminary Study with Representational Similarity Analysis</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>NeuroManagement and Intelligent Computing Method on Multimodal Interaction on - ICMI '19</t>
@@ -3228,16 +3567,22 @@
           <t>https://doi.org/10.1145/3357160.3357672</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3275,6 +3620,9 @@
           <t>https://doi.org/10.31234/osf.io/8dr23</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3285,11 +3633,13 @@
           <t>journal</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3327,16 +3677,22 @@
           <t>https://doi.org/10.1016/j.specom.2018.06.004</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3374,16 +3730,22 @@
           <t>https://doi.org/10.1016/j.neuroimage.2018.07.042</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3421,16 +3783,22 @@
           <t>https://doi.org/10.21437/SpeechProsody.2018-55</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3468,16 +3836,22 @@
           <t>https://doi.org/10.1002/hbm.23630</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3515,16 +3889,22 @@
           <t>https://doi.org/10.1016/j.snb.2017.01.052</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3562,16 +3942,22 @@
           <t>https://doi.org/10.1016/j.bandl.2017.04.005</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3609,16 +3995,22 @@
           <t>https://doi.org/10.1002/hbm.23633</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3656,16 +4048,22 @@
           <t>https://doi.org/10.1016/j.specom.2017.01.011</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3703,16 +4101,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2015.12.008</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3750,16 +4154,22 @@
           <t>https://doi.org/10.1037/xhp0000240</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3797,16 +4207,22 @@
           <t>https://doi.org/10.1037/xhp0000043</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3844,16 +4260,22 @@
           <t>https://doi.org/10.1016/j.cortex.2015.02.002</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3891,16 +4313,22 @@
           <t>https://doi.org/10.1080/23273798.2015.1005636</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3938,16 +4366,22 @@
           <t>https://doi.org/10.3389/fnhum.2014.00873</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3985,16 +4419,22 @@
           <t>https://doi.org/10.1093/scan/nst091</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4022,16 +4462,24 @@
           <t>conference-paper</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4069,16 +4517,22 @@
           <t>https://doi.org/10.1016/j.brainres.2012.10.042</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4116,16 +4570,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.06.009</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4163,16 +4623,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2013.07.021</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4210,16 +4676,22 @@
           <t>https://doi.org/10.1016/j.bandc.2012.11.002</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4257,16 +4729,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2012.04.016</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4304,16 +4782,22 @@
           <t>https://doi.org/10.1016/j.neuroscience.2011.10.035</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4351,16 +4835,22 @@
           <t>https://doi.org/10.1016/j.brainres.2011.06.061</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4398,16 +4888,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2010.02.001</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4445,16 +4941,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.01.013</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4492,16 +4994,22 @@
           <t>https://doi.org/10.1016/j.neuropsychologia.2009.02.020</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>0000-0002-5171-9774</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4868,8 +5376,6 @@
           <t>Professor · Doctoral Supervisor</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>主要从事心理与神经语言学的科学研究与人才培养工作。研究方向：心理与神经语言学、实验语言学、言语交际与言语障碍、嗓音编码与解码、神经语用学。</t>
